--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY578"/>
+  <dimension ref="A1:AY604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67610,6 +67610,2682 @@
       </c>
       <c r="AY578" t="inlineStr"/>
     </row>
+    <row r="579">
+      <c r="A579" t="n">
+        <v>119312223</v>
+      </c>
+      <c r="B579" t="n">
+        <v>97482</v>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E579" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr"/>
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>Verksmon, Verksmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q579" t="n">
+        <v>486946</v>
+      </c>
+      <c r="R579" t="n">
+        <v>7003956</v>
+      </c>
+      <c r="S579" t="n">
+        <v>10</v>
+      </c>
+      <c r="T579" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U579" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V579" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W579" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y579" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA579" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD579" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE579" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG579" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT579" t="inlineStr"/>
+      <c r="AW579" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AX579" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>119311396</v>
+      </c>
+      <c r="B580" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E580" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr"/>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>Torvalla naturreservat, Torvalla naturreservat, Jmt</t>
+        </is>
+      </c>
+      <c r="Q580" t="n">
+        <v>486995</v>
+      </c>
+      <c r="R580" t="n">
+        <v>7003925</v>
+      </c>
+      <c r="S580" t="n">
+        <v>20</v>
+      </c>
+      <c r="T580" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U580" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V580" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W580" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y580" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA580" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD580" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE580" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG580" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT580" t="inlineStr"/>
+      <c r="AW580" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX580" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>119308689</v>
+      </c>
+      <c r="B581" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E581" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P581" t="inlineStr">
+        <is>
+          <t>Verksmon, Verksmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q581" t="n">
+        <v>487060</v>
+      </c>
+      <c r="R581" t="n">
+        <v>7004115</v>
+      </c>
+      <c r="S581" t="n">
+        <v>3</v>
+      </c>
+      <c r="T581" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U581" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V581" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W581" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y581" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA581" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD581" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE581" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG581" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT581" t="inlineStr"/>
+      <c r="AW581" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AX581" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY581" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>119311630</v>
+      </c>
+      <c r="B582" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E582" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr"/>
+      <c r="P582" t="inlineStr">
+        <is>
+          <t>Verksmon, Verksmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q582" t="n">
+        <v>486944</v>
+      </c>
+      <c r="R582" t="n">
+        <v>7003933</v>
+      </c>
+      <c r="S582" t="n">
+        <v>5</v>
+      </c>
+      <c r="T582" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U582" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V582" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W582" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y582" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA582" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD582" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE582" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG582" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT582" t="inlineStr"/>
+      <c r="AW582" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AX582" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" t="n">
+        <v>119309495</v>
+      </c>
+      <c r="B583" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E583" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr"/>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P583" t="inlineStr">
+        <is>
+          <t>Verksmon, Verksmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q583" t="n">
+        <v>487056</v>
+      </c>
+      <c r="R583" t="n">
+        <v>7004063</v>
+      </c>
+      <c r="S583" t="n">
+        <v>3</v>
+      </c>
+      <c r="T583" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U583" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V583" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W583" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y583" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA583" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD583" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE583" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG583" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT583" t="inlineStr"/>
+      <c r="AW583" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AX583" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY583" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" t="n">
+        <v>119311723</v>
+      </c>
+      <c r="B584" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E584" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P584" t="inlineStr">
+        <is>
+          <t>Verksmon, Verksmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q584" t="n">
+        <v>486946</v>
+      </c>
+      <c r="R584" t="n">
+        <v>7003956</v>
+      </c>
+      <c r="S584" t="n">
+        <v>4</v>
+      </c>
+      <c r="T584" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U584" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V584" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W584" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y584" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA584" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD584" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE584" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG584" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT584" t="inlineStr"/>
+      <c r="AW584" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AX584" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY584" t="inlineStr"/>
+    </row>
+    <row r="585">
+      <c r="A585" t="n">
+        <v>119313051</v>
+      </c>
+      <c r="B585" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E585" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr"/>
+      <c r="P585" t="inlineStr">
+        <is>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q585" t="n">
+        <v>486843</v>
+      </c>
+      <c r="R585" t="n">
+        <v>7004053</v>
+      </c>
+      <c r="S585" t="n">
+        <v>10</v>
+      </c>
+      <c r="T585" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U585" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V585" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W585" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y585" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA585" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD585" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE585" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG585" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT585" t="inlineStr"/>
+      <c r="AW585" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX585" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY585" t="inlineStr"/>
+    </row>
+    <row r="586">
+      <c r="A586" t="n">
+        <v>119312547</v>
+      </c>
+      <c r="B586" t="n">
+        <v>97482</v>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E586" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr"/>
+      <c r="P586" t="inlineStr">
+        <is>
+          <t>Verksmon, Verksmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q586" t="n">
+        <v>487060</v>
+      </c>
+      <c r="R586" t="n">
+        <v>7004115</v>
+      </c>
+      <c r="S586" t="n">
+        <v>3</v>
+      </c>
+      <c r="T586" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U586" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V586" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W586" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y586" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA586" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD586" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE586" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG586" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT586" t="inlineStr"/>
+      <c r="AW586" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AX586" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY586" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" t="n">
+        <v>119312531</v>
+      </c>
+      <c r="B587" t="n">
+        <v>105456</v>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E587" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr"/>
+      <c r="P587" t="inlineStr">
+        <is>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q587" t="n">
+        <v>486896</v>
+      </c>
+      <c r="R587" t="n">
+        <v>7003946</v>
+      </c>
+      <c r="S587" t="n">
+        <v>10</v>
+      </c>
+      <c r="T587" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U587" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V587" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W587" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y587" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA587" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD587" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE587" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG587" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT587" t="inlineStr"/>
+      <c r="AW587" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX587" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY587" t="inlineStr"/>
+    </row>
+    <row r="588">
+      <c r="A588" t="n">
+        <v>119309241</v>
+      </c>
+      <c r="B588" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E588" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr"/>
+      <c r="P588" t="inlineStr">
+        <is>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q588" t="n">
+        <v>487066</v>
+      </c>
+      <c r="R588" t="n">
+        <v>7004042</v>
+      </c>
+      <c r="S588" t="n">
+        <v>50</v>
+      </c>
+      <c r="T588" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U588" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V588" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W588" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y588" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA588" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD588" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE588" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG588" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT588" t="inlineStr"/>
+      <c r="AW588" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX588" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY588" t="inlineStr"/>
+    </row>
+    <row r="589">
+      <c r="A589" t="n">
+        <v>119309475</v>
+      </c>
+      <c r="B589" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E589" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr"/>
+      <c r="P589" t="inlineStr">
+        <is>
+          <t>Verksmon, Verksmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q589" t="n">
+        <v>487092</v>
+      </c>
+      <c r="R589" t="n">
+        <v>7004027</v>
+      </c>
+      <c r="S589" t="n">
+        <v>10</v>
+      </c>
+      <c r="T589" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U589" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V589" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W589" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y589" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA589" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD589" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE589" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG589" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT589" t="inlineStr"/>
+      <c r="AW589" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX589" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY589" t="inlineStr"/>
+    </row>
+    <row r="590">
+      <c r="A590" t="n">
+        <v>119308823</v>
+      </c>
+      <c r="B590" t="n">
+        <v>91890</v>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E590" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr"/>
+      <c r="P590" t="inlineStr">
+        <is>
+          <t>Verksmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q590" t="n">
+        <v>487060</v>
+      </c>
+      <c r="R590" t="n">
+        <v>7004115</v>
+      </c>
+      <c r="S590" t="n">
+        <v>3</v>
+      </c>
+      <c r="T590" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U590" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V590" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W590" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y590" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA590" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD590" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE590" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG590" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT590" t="inlineStr"/>
+      <c r="AW590" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AX590" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY590" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" t="n">
+        <v>119311276</v>
+      </c>
+      <c r="B591" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E591" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr"/>
+      <c r="P591" t="inlineStr">
+        <is>
+          <t>Verksmon, Verksmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q591" t="n">
+        <v>487004</v>
+      </c>
+      <c r="R591" t="n">
+        <v>7003923</v>
+      </c>
+      <c r="S591" t="n">
+        <v>20</v>
+      </c>
+      <c r="T591" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U591" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V591" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W591" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y591" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA591" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD591" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE591" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG591" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT591" t="inlineStr"/>
+      <c r="AW591" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX591" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY591" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" t="n">
+        <v>119308870</v>
+      </c>
+      <c r="B592" t="n">
+        <v>94766</v>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E592" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr"/>
+      <c r="P592" t="inlineStr">
+        <is>
+          <t>Verksmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q592" t="n">
+        <v>487060</v>
+      </c>
+      <c r="R592" t="n">
+        <v>7004115</v>
+      </c>
+      <c r="S592" t="n">
+        <v>3</v>
+      </c>
+      <c r="T592" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U592" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V592" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W592" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y592" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA592" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD592" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE592" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG592" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT592" t="inlineStr"/>
+      <c r="AW592" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AX592" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY592" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" t="n">
+        <v>119312764</v>
+      </c>
+      <c r="B593" t="n">
+        <v>97482</v>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E593" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr"/>
+      <c r="P593" t="inlineStr">
+        <is>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q593" t="n">
+        <v>486807</v>
+      </c>
+      <c r="R593" t="n">
+        <v>7003950</v>
+      </c>
+      <c r="S593" t="n">
+        <v>10</v>
+      </c>
+      <c r="T593" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U593" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V593" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W593" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y593" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA593" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD593" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE593" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG593" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT593" t="inlineStr"/>
+      <c r="AW593" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX593" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY593" t="inlineStr"/>
+    </row>
+    <row r="594">
+      <c r="A594" t="n">
+        <v>119309185</v>
+      </c>
+      <c r="B594" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E594" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr"/>
+      <c r="P594" t="inlineStr">
+        <is>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q594" t="n">
+        <v>487054</v>
+      </c>
+      <c r="R594" t="n">
+        <v>7004058</v>
+      </c>
+      <c r="S594" t="n">
+        <v>10</v>
+      </c>
+      <c r="T594" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U594" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V594" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W594" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y594" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA594" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD594" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE594" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG594" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT594" t="inlineStr"/>
+      <c r="AW594" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX594" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY594" t="inlineStr"/>
+    </row>
+    <row r="595">
+      <c r="A595" t="n">
+        <v>119312982</v>
+      </c>
+      <c r="B595" t="n">
+        <v>91890</v>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E595" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr"/>
+      <c r="P595" t="inlineStr">
+        <is>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q595" t="n">
+        <v>486822</v>
+      </c>
+      <c r="R595" t="n">
+        <v>7004015</v>
+      </c>
+      <c r="S595" t="n">
+        <v>20</v>
+      </c>
+      <c r="T595" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U595" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V595" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W595" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y595" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA595" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD595" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE595" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG595" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT595" t="inlineStr"/>
+      <c r="AW595" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX595" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY595" t="inlineStr"/>
+    </row>
+    <row r="596">
+      <c r="A596" t="n">
+        <v>119310718</v>
+      </c>
+      <c r="B596" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E596" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr"/>
+      <c r="P596" t="inlineStr">
+        <is>
+          <t>Verksmon, Verksmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q596" t="n">
+        <v>487060</v>
+      </c>
+      <c r="R596" t="n">
+        <v>7004115</v>
+      </c>
+      <c r="S596" t="n">
+        <v>5</v>
+      </c>
+      <c r="T596" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U596" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V596" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W596" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y596" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA596" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD596" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE596" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG596" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT596" t="inlineStr"/>
+      <c r="AW596" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AX596" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY596" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" t="n">
+        <v>119312923</v>
+      </c>
+      <c r="B597" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E597" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr"/>
+      <c r="P597" t="inlineStr">
+        <is>
+          <t>Verksmon, Verksmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q597" t="n">
+        <v>487060</v>
+      </c>
+      <c r="R597" t="n">
+        <v>7004115</v>
+      </c>
+      <c r="S597" t="n">
+        <v>10</v>
+      </c>
+      <c r="T597" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U597" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V597" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W597" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y597" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA597" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD597" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE597" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG597" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT597" t="inlineStr"/>
+      <c r="AW597" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AX597" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY597" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" t="n">
+        <v>119310979</v>
+      </c>
+      <c r="B598" t="n">
+        <v>91890</v>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E598" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr"/>
+      <c r="P598" t="inlineStr">
+        <is>
+          <t>Verksmon, Verksmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q598" t="n">
+        <v>487043</v>
+      </c>
+      <c r="R598" t="n">
+        <v>7003935</v>
+      </c>
+      <c r="S598" t="n">
+        <v>20</v>
+      </c>
+      <c r="T598" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U598" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V598" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W598" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y598" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA598" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD598" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE598" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG598" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT598" t="inlineStr"/>
+      <c r="AW598" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX598" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY598" t="inlineStr"/>
+    </row>
+    <row r="599">
+      <c r="A599" t="n">
+        <v>119313079</v>
+      </c>
+      <c r="B599" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E599" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr"/>
+      <c r="P599" t="inlineStr">
+        <is>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q599" t="n">
+        <v>486834</v>
+      </c>
+      <c r="R599" t="n">
+        <v>7004097</v>
+      </c>
+      <c r="S599" t="n">
+        <v>10</v>
+      </c>
+      <c r="T599" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U599" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V599" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W599" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y599" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA599" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD599" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE599" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG599" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT599" t="inlineStr"/>
+      <c r="AW599" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX599" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY599" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" t="n">
+        <v>119312398</v>
+      </c>
+      <c r="B600" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E600" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr"/>
+      <c r="P600" t="inlineStr">
+        <is>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q600" t="n">
+        <v>486896</v>
+      </c>
+      <c r="R600" t="n">
+        <v>7003946</v>
+      </c>
+      <c r="S600" t="n">
+        <v>10</v>
+      </c>
+      <c r="T600" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U600" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V600" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W600" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y600" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA600" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD600" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE600" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG600" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT600" t="inlineStr"/>
+      <c r="AW600" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX600" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY600" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" t="n">
+        <v>119311193</v>
+      </c>
+      <c r="B601" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E601" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr"/>
+      <c r="P601" t="inlineStr">
+        <is>
+          <t>Verksmon, Verksmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q601" t="n">
+        <v>487004</v>
+      </c>
+      <c r="R601" t="n">
+        <v>7003923</v>
+      </c>
+      <c r="S601" t="n">
+        <v>20</v>
+      </c>
+      <c r="T601" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U601" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V601" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W601" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y601" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA601" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD601" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE601" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG601" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT601" t="inlineStr"/>
+      <c r="AW601" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX601" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY601" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" t="n">
+        <v>119312082</v>
+      </c>
+      <c r="B602" t="n">
+        <v>94766</v>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E602" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr"/>
+      <c r="P602" t="inlineStr">
+        <is>
+          <t>Verksmon, Verksmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q602" t="n">
+        <v>486946</v>
+      </c>
+      <c r="R602" t="n">
+        <v>7003956</v>
+      </c>
+      <c r="S602" t="n">
+        <v>10</v>
+      </c>
+      <c r="T602" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U602" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V602" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W602" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y602" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA602" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD602" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE602" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG602" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT602" t="inlineStr"/>
+      <c r="AW602" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AX602" t="inlineStr">
+        <is>
+          <t>Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY602" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" t="n">
+        <v>119311857</v>
+      </c>
+      <c r="B603" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E603" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr"/>
+      <c r="P603" t="inlineStr">
+        <is>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q603" t="n">
+        <v>486943</v>
+      </c>
+      <c r="R603" t="n">
+        <v>7003953</v>
+      </c>
+      <c r="S603" t="n">
+        <v>20</v>
+      </c>
+      <c r="T603" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U603" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V603" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W603" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y603" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA603" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD603" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE603" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG603" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT603" t="inlineStr"/>
+      <c r="AW603" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX603" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY603" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" t="n">
+        <v>119312412</v>
+      </c>
+      <c r="B604" t="n">
+        <v>97378</v>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E604" t="n">
+        <v>221063</v>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Trådfräken</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>Equisetum scirpoides</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>Michx.</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr"/>
+      <c r="P604" t="inlineStr">
+        <is>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q604" t="n">
+        <v>486896</v>
+      </c>
+      <c r="R604" t="n">
+        <v>7003946</v>
+      </c>
+      <c r="S604" t="n">
+        <v>10</v>
+      </c>
+      <c r="T604" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U604" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V604" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W604" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y604" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AA604" t="inlineStr">
+        <is>
+          <t>2024-08-24</t>
+        </is>
+      </c>
+      <c r="AD604" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE604" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG604" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT604" t="inlineStr"/>
+      <c r="AW604" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX604" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY604" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -68141,10 +68141,10 @@
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>119311723</v>
+        <v>119313051</v>
       </c>
       <c r="B584" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C584" t="inlineStr">
         <is>
@@ -68153,46 +68153,41 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E584" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I584" t="inlineStr"/>
-      <c r="K584" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P584" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q584" t="n">
-        <v>486946</v>
+        <v>486843</v>
       </c>
       <c r="R584" t="n">
-        <v>7003956</v>
+        <v>7004053</v>
       </c>
       <c r="S584" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T584" t="inlineStr">
         <is>
@@ -68236,22 +68231,22 @@
       <c r="AT584" t="inlineStr"/>
       <c r="AW584" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX584" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>119313051</v>
+        <v>119311723</v>
       </c>
       <c r="B585" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C585" t="inlineStr">
         <is>
@@ -68260,41 +68255,46 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E585" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P585" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q585" t="n">
-        <v>486843</v>
+        <v>486946</v>
       </c>
       <c r="R585" t="n">
-        <v>7004053</v>
+        <v>7003956</v>
       </c>
       <c r="S585" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T585" t="inlineStr">
         <is>
@@ -68338,12 +68338,12 @@
       <c r="AT585" t="inlineStr"/>
       <c r="AW585" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX585" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY585" t="inlineStr"/>
@@ -68962,10 +68962,10 @@
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>119308870</v>
+        <v>119312764</v>
       </c>
       <c r="B592" t="n">
-        <v>94766</v>
+        <v>97482</v>
       </c>
       <c r="C592" t="inlineStr">
         <is>
@@ -68978,37 +68978,37 @@
         </is>
       </c>
       <c r="E592" t="n">
-        <v>2809</v>
+        <v>222741</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I592" t="inlineStr"/>
       <c r="P592" t="inlineStr">
         <is>
-          <t>Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q592" t="n">
-        <v>487060</v>
+        <v>486807</v>
       </c>
       <c r="R592" t="n">
-        <v>7004115</v>
+        <v>7003950</v>
       </c>
       <c r="S592" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T592" t="inlineStr">
         <is>
@@ -69052,22 +69052,22 @@
       <c r="AT592" t="inlineStr"/>
       <c r="AW592" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX592" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>119312764</v>
+        <v>119309185</v>
       </c>
       <c r="B593" t="n">
-        <v>97482</v>
+        <v>98365</v>
       </c>
       <c r="C593" t="inlineStr">
         <is>
@@ -69076,25 +69076,25 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>222741</v>
+        <v>220787</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I593" t="inlineStr"/>
@@ -69104,10 +69104,10 @@
         </is>
       </c>
       <c r="Q593" t="n">
-        <v>486807</v>
+        <v>487054</v>
       </c>
       <c r="R593" t="n">
-        <v>7003950</v>
+        <v>7004058</v>
       </c>
       <c r="S593" t="n">
         <v>10</v>
@@ -69166,10 +69166,10 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>119309185</v>
+        <v>119312982</v>
       </c>
       <c r="B594" t="n">
-        <v>98365</v>
+        <v>91890</v>
       </c>
       <c r="C594" t="inlineStr">
         <is>
@@ -69178,25 +69178,25 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E594" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I594" t="inlineStr"/>
@@ -69206,13 +69206,13 @@
         </is>
       </c>
       <c r="Q594" t="n">
-        <v>487054</v>
+        <v>486822</v>
       </c>
       <c r="R594" t="n">
-        <v>7004058</v>
+        <v>7004015</v>
       </c>
       <c r="S594" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T594" t="inlineStr">
         <is>
@@ -69268,10 +69268,10 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>119312982</v>
+        <v>119308870</v>
       </c>
       <c r="B595" t="n">
-        <v>91890</v>
+        <v>94766</v>
       </c>
       <c r="C595" t="inlineStr">
         <is>
@@ -69284,37 +69284,37 @@
         </is>
       </c>
       <c r="E595" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I595" t="inlineStr"/>
       <c r="P595" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q595" t="n">
-        <v>486822</v>
+        <v>487060</v>
       </c>
       <c r="R595" t="n">
-        <v>7004015</v>
+        <v>7004115</v>
       </c>
       <c r="S595" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T595" t="inlineStr">
         <is>
@@ -69358,12 +69358,12 @@
       <c r="AT595" t="inlineStr"/>
       <c r="AW595" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX595" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY595" t="inlineStr"/>

--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -68962,10 +68962,10 @@
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>119312764</v>
+        <v>119308870</v>
       </c>
       <c r="B592" t="n">
-        <v>97482</v>
+        <v>94766</v>
       </c>
       <c r="C592" t="inlineStr">
         <is>
@@ -68978,37 +68978,37 @@
         </is>
       </c>
       <c r="E592" t="n">
-        <v>222741</v>
+        <v>2809</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I592" t="inlineStr"/>
       <c r="P592" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q592" t="n">
-        <v>486807</v>
+        <v>487060</v>
       </c>
       <c r="R592" t="n">
-        <v>7003950</v>
+        <v>7004115</v>
       </c>
       <c r="S592" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T592" t="inlineStr">
         <is>
@@ -69052,22 +69052,22 @@
       <c r="AT592" t="inlineStr"/>
       <c r="AW592" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX592" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>119309185</v>
+        <v>119312764</v>
       </c>
       <c r="B593" t="n">
-        <v>98365</v>
+        <v>97482</v>
       </c>
       <c r="C593" t="inlineStr">
         <is>
@@ -69076,25 +69076,25 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>220787</v>
+        <v>222741</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I593" t="inlineStr"/>
@@ -69104,10 +69104,10 @@
         </is>
       </c>
       <c r="Q593" t="n">
-        <v>487054</v>
+        <v>486807</v>
       </c>
       <c r="R593" t="n">
-        <v>7004058</v>
+        <v>7003950</v>
       </c>
       <c r="S593" t="n">
         <v>10</v>
@@ -69166,10 +69166,10 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>119312982</v>
+        <v>119309185</v>
       </c>
       <c r="B594" t="n">
-        <v>91890</v>
+        <v>98365</v>
       </c>
       <c r="C594" t="inlineStr">
         <is>
@@ -69178,25 +69178,25 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E594" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I594" t="inlineStr"/>
@@ -69206,13 +69206,13 @@
         </is>
       </c>
       <c r="Q594" t="n">
-        <v>486822</v>
+        <v>487054</v>
       </c>
       <c r="R594" t="n">
-        <v>7004015</v>
+        <v>7004058</v>
       </c>
       <c r="S594" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T594" t="inlineStr">
         <is>
@@ -69268,10 +69268,10 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>119308870</v>
+        <v>119312982</v>
       </c>
       <c r="B595" t="n">
-        <v>94766</v>
+        <v>91890</v>
       </c>
       <c r="C595" t="inlineStr">
         <is>
@@ -69284,37 +69284,37 @@
         </is>
       </c>
       <c r="E595" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I595" t="inlineStr"/>
       <c r="P595" t="inlineStr">
         <is>
-          <t>Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q595" t="n">
-        <v>487060</v>
+        <v>486822</v>
       </c>
       <c r="R595" t="n">
-        <v>7004115</v>
+        <v>7004015</v>
       </c>
       <c r="S595" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T595" t="inlineStr">
         <is>
@@ -69358,12 +69358,12 @@
       <c r="AT595" t="inlineStr"/>
       <c r="AW595" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX595" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY595" t="inlineStr"/>

--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -67612,10 +67612,10 @@
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>119312223</v>
+        <v>119311396</v>
       </c>
       <c r="B579" t="n">
-        <v>97482</v>
+        <v>98365</v>
       </c>
       <c r="C579" t="inlineStr">
         <is>
@@ -67624,41 +67624,41 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E579" t="n">
-        <v>222741</v>
+        <v>220787</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I579" t="inlineStr"/>
       <c r="P579" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Torvalla naturreservat, Torvalla naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q579" t="n">
-        <v>486946</v>
+        <v>486995</v>
       </c>
       <c r="R579" t="n">
-        <v>7003956</v>
+        <v>7003925</v>
       </c>
       <c r="S579" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T579" t="inlineStr">
         <is>
@@ -67702,22 +67702,22 @@
       <c r="AT579" t="inlineStr"/>
       <c r="AW579" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX579" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>119311396</v>
+        <v>119312223</v>
       </c>
       <c r="B580" t="n">
-        <v>98365</v>
+        <v>97482</v>
       </c>
       <c r="C580" t="inlineStr">
         <is>
@@ -67726,41 +67726,41 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E580" t="n">
-        <v>220787</v>
+        <v>222741</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I580" t="inlineStr"/>
       <c r="P580" t="inlineStr">
         <is>
-          <t>Torvalla naturreservat, Torvalla naturreservat, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q580" t="n">
-        <v>486995</v>
+        <v>486946</v>
       </c>
       <c r="R580" t="n">
-        <v>7003925</v>
+        <v>7003956</v>
       </c>
       <c r="S580" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T580" t="inlineStr">
         <is>
@@ -67804,12 +67804,12 @@
       <c r="AT580" t="inlineStr"/>
       <c r="AW580" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX580" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY580" t="inlineStr"/>

--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -67612,10 +67612,10 @@
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>119311396</v>
+        <v>119313051</v>
       </c>
       <c r="B579" t="n">
-        <v>98365</v>
+        <v>78769</v>
       </c>
       <c r="C579" t="inlineStr">
         <is>
@@ -67624,41 +67624,41 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E579" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I579" t="inlineStr"/>
       <c r="P579" t="inlineStr">
         <is>
-          <t>Torvalla naturreservat, Torvalla naturreservat, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q579" t="n">
-        <v>486995</v>
+        <v>486843</v>
       </c>
       <c r="R579" t="n">
-        <v>7003925</v>
+        <v>7004053</v>
       </c>
       <c r="S579" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T579" t="inlineStr">
         <is>
@@ -67714,10 +67714,10 @@
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>119312223</v>
+        <v>119309504</v>
       </c>
       <c r="B580" t="n">
-        <v>97482</v>
+        <v>98368</v>
       </c>
       <c r="C580" t="inlineStr">
         <is>
@@ -67726,25 +67726,25 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E580" t="n">
-        <v>222741</v>
+        <v>220787</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I580" t="inlineStr"/>
@@ -67754,13 +67754,13 @@
         </is>
       </c>
       <c r="Q580" t="n">
-        <v>486946</v>
+        <v>487056</v>
       </c>
       <c r="R580" t="n">
-        <v>7003956</v>
+        <v>7004063</v>
       </c>
       <c r="S580" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T580" t="inlineStr">
         <is>
@@ -67816,10 +67816,10 @@
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>119308689</v>
+        <v>119312398</v>
       </c>
       <c r="B581" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C581" t="inlineStr">
         <is>
@@ -67849,34 +67849,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I581" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J581" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K581" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I581" t="inlineStr"/>
       <c r="P581" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q581" t="n">
-        <v>487060</v>
+        <v>486896</v>
       </c>
       <c r="R581" t="n">
-        <v>7004115</v>
+        <v>7003946</v>
       </c>
       <c r="S581" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T581" t="inlineStr">
         <is>
@@ -67920,22 +67906,22 @@
       <c r="AT581" t="inlineStr"/>
       <c r="AW581" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX581" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>119311630</v>
+        <v>119311193</v>
       </c>
       <c r="B582" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C582" t="inlineStr">
         <is>
@@ -67972,13 +67958,13 @@
         </is>
       </c>
       <c r="Q582" t="n">
-        <v>486944</v>
+        <v>487004</v>
       </c>
       <c r="R582" t="n">
-        <v>7003933</v>
+        <v>7003923</v>
       </c>
       <c r="S582" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T582" t="inlineStr">
         <is>
@@ -68022,22 +68008,22 @@
       <c r="AT582" t="inlineStr"/>
       <c r="AW582" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX582" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY582" t="inlineStr"/>
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>119309495</v>
+        <v>119312412</v>
       </c>
       <c r="B583" t="n">
-        <v>98365</v>
+        <v>97381</v>
       </c>
       <c r="C583" t="inlineStr">
         <is>
@@ -68046,46 +68032,41 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E583" t="n">
-        <v>220787</v>
+        <v>221063</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I583" t="inlineStr"/>
-      <c r="J583" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P583" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q583" t="n">
-        <v>487056</v>
+        <v>486896</v>
       </c>
       <c r="R583" t="n">
-        <v>7004063</v>
+        <v>7003946</v>
       </c>
       <c r="S583" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T583" t="inlineStr">
         <is>
@@ -68129,22 +68110,22 @@
       <c r="AT583" t="inlineStr"/>
       <c r="AW583" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX583" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>119313051</v>
+        <v>119312223</v>
       </c>
       <c r="B584" t="n">
-        <v>78766</v>
+        <v>97485</v>
       </c>
       <c r="C584" t="inlineStr">
         <is>
@@ -68153,38 +68134,38 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E584" t="n">
-        <v>6425</v>
+        <v>222741</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I584" t="inlineStr"/>
       <c r="P584" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q584" t="n">
-        <v>486843</v>
+        <v>486946</v>
       </c>
       <c r="R584" t="n">
-        <v>7004053</v>
+        <v>7003956</v>
       </c>
       <c r="S584" t="n">
         <v>10</v>
@@ -68231,22 +68212,22 @@
       <c r="AT584" t="inlineStr"/>
       <c r="AW584" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX584" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>119311723</v>
+        <v>119308623</v>
       </c>
       <c r="B585" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C585" t="inlineStr">
         <is>
@@ -68276,7 +68257,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I585" t="inlineStr"/>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K585" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -68288,13 +68278,13 @@
         </is>
       </c>
       <c r="Q585" t="n">
-        <v>486946</v>
+        <v>487060</v>
       </c>
       <c r="R585" t="n">
-        <v>7003956</v>
+        <v>7004115</v>
       </c>
       <c r="S585" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T585" t="inlineStr">
         <is>
@@ -68350,10 +68340,10 @@
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>119312547</v>
+        <v>119312531</v>
       </c>
       <c r="B586" t="n">
-        <v>97482</v>
+        <v>105459</v>
       </c>
       <c r="C586" t="inlineStr">
         <is>
@@ -68366,37 +68356,37 @@
         </is>
       </c>
       <c r="E586" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I586" t="inlineStr"/>
       <c r="P586" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q586" t="n">
-        <v>487060</v>
+        <v>486896</v>
       </c>
       <c r="R586" t="n">
-        <v>7004115</v>
+        <v>7003946</v>
       </c>
       <c r="S586" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T586" t="inlineStr">
         <is>
@@ -68440,22 +68430,22 @@
       <c r="AT586" t="inlineStr"/>
       <c r="AW586" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX586" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>119312531</v>
+        <v>119311396</v>
       </c>
       <c r="B587" t="n">
-        <v>105456</v>
+        <v>98368</v>
       </c>
       <c r="C587" t="inlineStr">
         <is>
@@ -68464,41 +68454,41 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E587" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I587" t="inlineStr"/>
       <c r="P587" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Torvalla naturreservat, Torvalla naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q587" t="n">
-        <v>486896</v>
+        <v>486995</v>
       </c>
       <c r="R587" t="n">
-        <v>7003946</v>
+        <v>7003925</v>
       </c>
       <c r="S587" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T587" t="inlineStr">
         <is>
@@ -68554,10 +68544,10 @@
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>119309241</v>
+        <v>119310718</v>
       </c>
       <c r="B588" t="n">
-        <v>57631</v>
+        <v>78769</v>
       </c>
       <c r="C588" t="inlineStr">
         <is>
@@ -68570,37 +68560,37 @@
         </is>
       </c>
       <c r="E588" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I588" t="inlineStr"/>
       <c r="P588" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q588" t="n">
-        <v>487066</v>
+        <v>487060</v>
       </c>
       <c r="R588" t="n">
-        <v>7004042</v>
+        <v>7004115</v>
       </c>
       <c r="S588" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T588" t="inlineStr">
         <is>
@@ -68644,22 +68634,22 @@
       <c r="AT588" t="inlineStr"/>
       <c r="AW588" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX588" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>119309475</v>
+        <v>119311723</v>
       </c>
       <c r="B589" t="n">
-        <v>78766</v>
+        <v>98368</v>
       </c>
       <c r="C589" t="inlineStr">
         <is>
@@ -68668,41 +68658,46 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E589" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P589" t="inlineStr">
         <is>
           <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q589" t="n">
-        <v>487092</v>
+        <v>486946</v>
       </c>
       <c r="R589" t="n">
-        <v>7004027</v>
+        <v>7003956</v>
       </c>
       <c r="S589" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T589" t="inlineStr">
         <is>
@@ -68746,22 +68741,22 @@
       <c r="AT589" t="inlineStr"/>
       <c r="AW589" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX589" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>119308823</v>
+        <v>119310979</v>
       </c>
       <c r="B590" t="n">
-        <v>91890</v>
+        <v>91893</v>
       </c>
       <c r="C590" t="inlineStr">
         <is>
@@ -68794,17 +68789,17 @@
       <c r="I590" t="inlineStr"/>
       <c r="P590" t="inlineStr">
         <is>
-          <t>Verksmon, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q590" t="n">
-        <v>487060</v>
+        <v>487043</v>
       </c>
       <c r="R590" t="n">
-        <v>7004115</v>
+        <v>7003935</v>
       </c>
       <c r="S590" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T590" t="inlineStr">
         <is>
@@ -68848,22 +68843,22 @@
       <c r="AT590" t="inlineStr"/>
       <c r="AW590" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX590" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY590" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>119311276</v>
+        <v>119308870</v>
       </c>
       <c r="B591" t="n">
-        <v>90952</v>
+        <v>94769</v>
       </c>
       <c r="C591" t="inlineStr">
         <is>
@@ -68872,41 +68867,41 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E591" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I591" t="inlineStr"/>
       <c r="P591" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q591" t="n">
-        <v>487004</v>
+        <v>487060</v>
       </c>
       <c r="R591" t="n">
-        <v>7003923</v>
+        <v>7004115</v>
       </c>
       <c r="S591" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T591" t="inlineStr">
         <is>
@@ -68950,22 +68945,22 @@
       <c r="AT591" t="inlineStr"/>
       <c r="AW591" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX591" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>119308870</v>
+        <v>119309475</v>
       </c>
       <c r="B592" t="n">
-        <v>94766</v>
+        <v>78769</v>
       </c>
       <c r="C592" t="inlineStr">
         <is>
@@ -68974,41 +68969,41 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E592" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I592" t="inlineStr"/>
       <c r="P592" t="inlineStr">
         <is>
-          <t>Verksmon, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q592" t="n">
-        <v>487060</v>
+        <v>487092</v>
       </c>
       <c r="R592" t="n">
-        <v>7004115</v>
+        <v>7004027</v>
       </c>
       <c r="S592" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T592" t="inlineStr">
         <is>
@@ -69052,12 +69047,12 @@
       <c r="AT592" t="inlineStr"/>
       <c r="AW592" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX592" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY592" t="inlineStr"/>
@@ -69067,7 +69062,7 @@
         <v>119312764</v>
       </c>
       <c r="B593" t="n">
-        <v>97482</v>
+        <v>97485</v>
       </c>
       <c r="C593" t="inlineStr">
         <is>
@@ -69166,10 +69161,10 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>119309185</v>
+        <v>119311276</v>
       </c>
       <c r="B594" t="n">
-        <v>98365</v>
+        <v>90955</v>
       </c>
       <c r="C594" t="inlineStr">
         <is>
@@ -69178,41 +69173,41 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E594" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I594" t="inlineStr"/>
       <c r="P594" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q594" t="n">
-        <v>487054</v>
+        <v>487004</v>
       </c>
       <c r="R594" t="n">
-        <v>7004058</v>
+        <v>7003923</v>
       </c>
       <c r="S594" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T594" t="inlineStr">
         <is>
@@ -69268,10 +69263,10 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>119312982</v>
+        <v>119311857</v>
       </c>
       <c r="B595" t="n">
-        <v>91890</v>
+        <v>90955</v>
       </c>
       <c r="C595" t="inlineStr">
         <is>
@@ -69280,25 +69275,25 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E595" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I595" t="inlineStr"/>
@@ -69308,10 +69303,10 @@
         </is>
       </c>
       <c r="Q595" t="n">
-        <v>486822</v>
+        <v>486943</v>
       </c>
       <c r="R595" t="n">
-        <v>7004015</v>
+        <v>7003953</v>
       </c>
       <c r="S595" t="n">
         <v>20</v>
@@ -69370,10 +69365,10 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>119310718</v>
+        <v>119308823</v>
       </c>
       <c r="B596" t="n">
-        <v>78766</v>
+        <v>91893</v>
       </c>
       <c r="C596" t="inlineStr">
         <is>
@@ -69382,31 +69377,31 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E596" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I596" t="inlineStr"/>
       <c r="P596" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q596" t="n">
@@ -69416,7 +69411,7 @@
         <v>7004115</v>
       </c>
       <c r="S596" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T596" t="inlineStr">
         <is>
@@ -69472,10 +69467,10 @@
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>119312923</v>
+        <v>119311630</v>
       </c>
       <c r="B597" t="n">
-        <v>57631</v>
+        <v>78769</v>
       </c>
       <c r="C597" t="inlineStr">
         <is>
@@ -69488,21 +69483,21 @@
         </is>
       </c>
       <c r="E597" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I597" t="inlineStr"/>
@@ -69512,13 +69507,13 @@
         </is>
       </c>
       <c r="Q597" t="n">
-        <v>487060</v>
+        <v>486944</v>
       </c>
       <c r="R597" t="n">
-        <v>7004115</v>
+        <v>7003933</v>
       </c>
       <c r="S597" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T597" t="inlineStr">
         <is>
@@ -69574,10 +69569,10 @@
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>119310979</v>
+        <v>119309241</v>
       </c>
       <c r="B598" t="n">
-        <v>91890</v>
+        <v>57634</v>
       </c>
       <c r="C598" t="inlineStr">
         <is>
@@ -69586,41 +69581,41 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E598" t="n">
-        <v>4769</v>
+        <v>103021</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I598" t="inlineStr"/>
       <c r="P598" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q598" t="n">
-        <v>487043</v>
+        <v>487066</v>
       </c>
       <c r="R598" t="n">
-        <v>7003935</v>
+        <v>7004042</v>
       </c>
       <c r="S598" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T598" t="inlineStr">
         <is>
@@ -69676,10 +69671,10 @@
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>119313079</v>
+        <v>119312082</v>
       </c>
       <c r="B599" t="n">
-        <v>78766</v>
+        <v>94769</v>
       </c>
       <c r="C599" t="inlineStr">
         <is>
@@ -69688,38 +69683,38 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E599" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I599" t="inlineStr"/>
       <c r="P599" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q599" t="n">
-        <v>486834</v>
+        <v>486946</v>
       </c>
       <c r="R599" t="n">
-        <v>7004097</v>
+        <v>7003956</v>
       </c>
       <c r="S599" t="n">
         <v>10</v>
@@ -69766,22 +69761,22 @@
       <c r="AT599" t="inlineStr"/>
       <c r="AW599" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX599" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>119312398</v>
+        <v>119312923</v>
       </c>
       <c r="B600" t="n">
-        <v>98365</v>
+        <v>57634</v>
       </c>
       <c r="C600" t="inlineStr">
         <is>
@@ -69790,38 +69785,38 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E600" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I600" t="inlineStr"/>
       <c r="P600" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q600" t="n">
-        <v>486896</v>
+        <v>487060</v>
       </c>
       <c r="R600" t="n">
-        <v>7003946</v>
+        <v>7004115</v>
       </c>
       <c r="S600" t="n">
         <v>10</v>
@@ -69868,22 +69863,22 @@
       <c r="AT600" t="inlineStr"/>
       <c r="AW600" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX600" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>119311193</v>
+        <v>119309185</v>
       </c>
       <c r="B601" t="n">
-        <v>78766</v>
+        <v>98368</v>
       </c>
       <c r="C601" t="inlineStr">
         <is>
@@ -69892,41 +69887,41 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E601" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I601" t="inlineStr"/>
       <c r="P601" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q601" t="n">
-        <v>487004</v>
+        <v>487054</v>
       </c>
       <c r="R601" t="n">
-        <v>7003923</v>
+        <v>7004058</v>
       </c>
       <c r="S601" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T601" t="inlineStr">
         <is>
@@ -69982,10 +69977,10 @@
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>119312082</v>
+        <v>119312547</v>
       </c>
       <c r="B602" t="n">
-        <v>94766</v>
+        <v>97485</v>
       </c>
       <c r="C602" t="inlineStr">
         <is>
@@ -69998,21 +69993,21 @@
         </is>
       </c>
       <c r="E602" t="n">
-        <v>2809</v>
+        <v>222741</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I602" t="inlineStr"/>
@@ -70022,13 +70017,13 @@
         </is>
       </c>
       <c r="Q602" t="n">
-        <v>486946</v>
+        <v>487060</v>
       </c>
       <c r="R602" t="n">
-        <v>7003956</v>
+        <v>7004115</v>
       </c>
       <c r="S602" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T602" t="inlineStr">
         <is>
@@ -70084,10 +70079,10 @@
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>119311857</v>
+        <v>119312982</v>
       </c>
       <c r="B603" t="n">
-        <v>90952</v>
+        <v>91893</v>
       </c>
       <c r="C603" t="inlineStr">
         <is>
@@ -70096,25 +70091,25 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E603" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I603" t="inlineStr"/>
@@ -70124,10 +70119,10 @@
         </is>
       </c>
       <c r="Q603" t="n">
-        <v>486943</v>
+        <v>486822</v>
       </c>
       <c r="R603" t="n">
-        <v>7003953</v>
+        <v>7004015</v>
       </c>
       <c r="S603" t="n">
         <v>20</v>
@@ -70186,10 +70181,10 @@
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>119312412</v>
+        <v>119313079</v>
       </c>
       <c r="B604" t="n">
-        <v>97378</v>
+        <v>78769</v>
       </c>
       <c r="C604" t="inlineStr">
         <is>
@@ -70198,25 +70193,25 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E604" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I604" t="inlineStr"/>
@@ -70226,10 +70221,10 @@
         </is>
       </c>
       <c r="Q604" t="n">
-        <v>486896</v>
+        <v>486834</v>
       </c>
       <c r="R604" t="n">
-        <v>7003946</v>
+        <v>7004097</v>
       </c>
       <c r="S604" t="n">
         <v>10</v>

--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -67612,10 +67612,10 @@
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>119313051</v>
+        <v>119311276</v>
       </c>
       <c r="B579" t="n">
-        <v>78769</v>
+        <v>90957</v>
       </c>
       <c r="C579" t="inlineStr">
         <is>
@@ -67628,37 +67628,37 @@
         </is>
       </c>
       <c r="E579" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I579" t="inlineStr"/>
       <c r="P579" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q579" t="n">
-        <v>486843</v>
+        <v>487004</v>
       </c>
       <c r="R579" t="n">
-        <v>7004053</v>
+        <v>7003923</v>
       </c>
       <c r="S579" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T579" t="inlineStr">
         <is>
@@ -67714,10 +67714,10 @@
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>119309504</v>
+        <v>119312082</v>
       </c>
       <c r="B580" t="n">
-        <v>98368</v>
+        <v>94771</v>
       </c>
       <c r="C580" t="inlineStr">
         <is>
@@ -67726,25 +67726,25 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E580" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I580" t="inlineStr"/>
@@ -67754,13 +67754,13 @@
         </is>
       </c>
       <c r="Q580" t="n">
-        <v>487056</v>
+        <v>486946</v>
       </c>
       <c r="R580" t="n">
-        <v>7004063</v>
+        <v>7003956</v>
       </c>
       <c r="S580" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T580" t="inlineStr">
         <is>
@@ -67816,10 +67816,10 @@
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>119312398</v>
+        <v>119312537</v>
       </c>
       <c r="B581" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C581" t="inlineStr">
         <is>
@@ -67852,17 +67852,17 @@
       <c r="I581" t="inlineStr"/>
       <c r="P581" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q581" t="n">
-        <v>486896</v>
+        <v>487060</v>
       </c>
       <c r="R581" t="n">
-        <v>7003946</v>
+        <v>7004115</v>
       </c>
       <c r="S581" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T581" t="inlineStr">
         <is>
@@ -67906,22 +67906,22 @@
       <c r="AT581" t="inlineStr"/>
       <c r="AW581" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX581" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>119311193</v>
+        <v>119309185</v>
       </c>
       <c r="B582" t="n">
-        <v>78769</v>
+        <v>98370</v>
       </c>
       <c r="C582" t="inlineStr">
         <is>
@@ -67930,41 +67930,41 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E582" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I582" t="inlineStr"/>
       <c r="P582" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q582" t="n">
-        <v>487004</v>
+        <v>487054</v>
       </c>
       <c r="R582" t="n">
-        <v>7003923</v>
+        <v>7004058</v>
       </c>
       <c r="S582" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T582" t="inlineStr">
         <is>
@@ -68020,10 +68020,10 @@
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>119312412</v>
+        <v>119310718</v>
       </c>
       <c r="B583" t="n">
-        <v>97381</v>
+        <v>78771</v>
       </c>
       <c r="C583" t="inlineStr">
         <is>
@@ -68032,41 +68032,41 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E583" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I583" t="inlineStr"/>
       <c r="P583" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q583" t="n">
-        <v>486896</v>
+        <v>487060</v>
       </c>
       <c r="R583" t="n">
-        <v>7003946</v>
+        <v>7004115</v>
       </c>
       <c r="S583" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T583" t="inlineStr">
         <is>
@@ -68110,22 +68110,22 @@
       <c r="AT583" t="inlineStr"/>
       <c r="AW583" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX583" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY583" t="inlineStr"/>
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>119312223</v>
+        <v>119309241</v>
       </c>
       <c r="B584" t="n">
-        <v>97485</v>
+        <v>57634</v>
       </c>
       <c r="C584" t="inlineStr">
         <is>
@@ -68134,41 +68134,41 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E584" t="n">
-        <v>222741</v>
+        <v>103021</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I584" t="inlineStr"/>
       <c r="P584" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q584" t="n">
-        <v>486946</v>
+        <v>487066</v>
       </c>
       <c r="R584" t="n">
-        <v>7003956</v>
+        <v>7004042</v>
       </c>
       <c r="S584" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T584" t="inlineStr">
         <is>
@@ -68212,22 +68212,22 @@
       <c r="AT584" t="inlineStr"/>
       <c r="AW584" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX584" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>119308623</v>
+        <v>119312923</v>
       </c>
       <c r="B585" t="n">
-        <v>98368</v>
+        <v>57634</v>
       </c>
       <c r="C585" t="inlineStr">
         <is>
@@ -68236,42 +68236,28 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E585" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I585" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J585" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K585" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr"/>
       <c r="P585" t="inlineStr">
         <is>
           <t>Verksmon, Verksmon, Jmt</t>
@@ -68284,7 +68270,7 @@
         <v>7004115</v>
       </c>
       <c r="S585" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T585" t="inlineStr">
         <is>
@@ -68340,10 +68326,10 @@
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>119312531</v>
+        <v>119312434</v>
       </c>
       <c r="B586" t="n">
-        <v>105459</v>
+        <v>105461</v>
       </c>
       <c r="C586" t="inlineStr">
         <is>
@@ -68442,10 +68428,10 @@
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>119311396</v>
+        <v>119312223</v>
       </c>
       <c r="B587" t="n">
-        <v>98368</v>
+        <v>97487</v>
       </c>
       <c r="C587" t="inlineStr">
         <is>
@@ -68454,41 +68440,41 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E587" t="n">
-        <v>220787</v>
+        <v>222741</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I587" t="inlineStr"/>
       <c r="P587" t="inlineStr">
         <is>
-          <t>Torvalla naturreservat, Torvalla naturreservat, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q587" t="n">
-        <v>486995</v>
+        <v>486946</v>
       </c>
       <c r="R587" t="n">
-        <v>7003925</v>
+        <v>7003956</v>
       </c>
       <c r="S587" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T587" t="inlineStr">
         <is>
@@ -68532,22 +68518,22 @@
       <c r="AT587" t="inlineStr"/>
       <c r="AW587" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX587" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>119310718</v>
+        <v>119310979</v>
       </c>
       <c r="B588" t="n">
-        <v>78769</v>
+        <v>91895</v>
       </c>
       <c r="C588" t="inlineStr">
         <is>
@@ -68556,25 +68542,25 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E588" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I588" t="inlineStr"/>
@@ -68584,13 +68570,13 @@
         </is>
       </c>
       <c r="Q588" t="n">
-        <v>487060</v>
+        <v>487043</v>
       </c>
       <c r="R588" t="n">
-        <v>7004115</v>
+        <v>7003935</v>
       </c>
       <c r="S588" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T588" t="inlineStr">
         <is>
@@ -68634,22 +68620,22 @@
       <c r="AT588" t="inlineStr"/>
       <c r="AW588" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX588" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>119311723</v>
+        <v>119308823</v>
       </c>
       <c r="B589" t="n">
-        <v>98368</v>
+        <v>91895</v>
       </c>
       <c r="C589" t="inlineStr">
         <is>
@@ -68658,46 +68644,41 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E589" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I589" t="inlineStr"/>
-      <c r="K589" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P589" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q589" t="n">
-        <v>486946</v>
+        <v>487060</v>
       </c>
       <c r="R589" t="n">
-        <v>7003956</v>
+        <v>7004115</v>
       </c>
       <c r="S589" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T589" t="inlineStr">
         <is>
@@ -68753,10 +68734,10 @@
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>119310979</v>
+        <v>119313051</v>
       </c>
       <c r="B590" t="n">
-        <v>91893</v>
+        <v>78771</v>
       </c>
       <c r="C590" t="inlineStr">
         <is>
@@ -68765,41 +68746,41 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E590" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I590" t="inlineStr"/>
       <c r="P590" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q590" t="n">
-        <v>487043</v>
+        <v>486843</v>
       </c>
       <c r="R590" t="n">
-        <v>7003935</v>
+        <v>7004053</v>
       </c>
       <c r="S590" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T590" t="inlineStr">
         <is>
@@ -68855,10 +68836,10 @@
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>119308870</v>
+        <v>119309475</v>
       </c>
       <c r="B591" t="n">
-        <v>94769</v>
+        <v>78771</v>
       </c>
       <c r="C591" t="inlineStr">
         <is>
@@ -68867,41 +68848,41 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E591" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I591" t="inlineStr"/>
       <c r="P591" t="inlineStr">
         <is>
-          <t>Verksmon, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q591" t="n">
-        <v>487060</v>
+        <v>487092</v>
       </c>
       <c r="R591" t="n">
-        <v>7004115</v>
+        <v>7004027</v>
       </c>
       <c r="S591" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T591" t="inlineStr">
         <is>
@@ -68945,22 +68926,22 @@
       <c r="AT591" t="inlineStr"/>
       <c r="AW591" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX591" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>119309475</v>
+        <v>119311193</v>
       </c>
       <c r="B592" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C592" t="inlineStr">
         <is>
@@ -68997,13 +68978,13 @@
         </is>
       </c>
       <c r="Q592" t="n">
-        <v>487092</v>
+        <v>487004</v>
       </c>
       <c r="R592" t="n">
-        <v>7004027</v>
+        <v>7003923</v>
       </c>
       <c r="S592" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T592" t="inlineStr">
         <is>
@@ -69059,10 +69040,10 @@
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>119312764</v>
+        <v>119311723</v>
       </c>
       <c r="B593" t="n">
-        <v>97485</v>
+        <v>98370</v>
       </c>
       <c r="C593" t="inlineStr">
         <is>
@@ -69071,41 +69052,46 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>222741</v>
+        <v>220787</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P593" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q593" t="n">
-        <v>486807</v>
+        <v>486946</v>
       </c>
       <c r="R593" t="n">
-        <v>7003950</v>
+        <v>7003956</v>
       </c>
       <c r="S593" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T593" t="inlineStr">
         <is>
@@ -69149,22 +69135,22 @@
       <c r="AT593" t="inlineStr"/>
       <c r="AW593" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX593" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>119311276</v>
+        <v>119311857</v>
       </c>
       <c r="B594" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C594" t="inlineStr">
         <is>
@@ -69197,14 +69183,14 @@
       <c r="I594" t="inlineStr"/>
       <c r="P594" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q594" t="n">
-        <v>487004</v>
+        <v>486943</v>
       </c>
       <c r="R594" t="n">
-        <v>7003923</v>
+        <v>7003953</v>
       </c>
       <c r="S594" t="n">
         <v>20</v>
@@ -69263,10 +69249,10 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>119311857</v>
+        <v>119309504</v>
       </c>
       <c r="B595" t="n">
-        <v>90955</v>
+        <v>98370</v>
       </c>
       <c r="C595" t="inlineStr">
         <is>
@@ -69275,41 +69261,41 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E595" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I595" t="inlineStr"/>
       <c r="P595" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q595" t="n">
-        <v>486943</v>
+        <v>487056</v>
       </c>
       <c r="R595" t="n">
-        <v>7003953</v>
+        <v>7004063</v>
       </c>
       <c r="S595" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T595" t="inlineStr">
         <is>
@@ -69353,22 +69339,22 @@
       <c r="AT595" t="inlineStr"/>
       <c r="AW595" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX595" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY595" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>119308823</v>
+        <v>119311396</v>
       </c>
       <c r="B596" t="n">
-        <v>91893</v>
+        <v>98370</v>
       </c>
       <c r="C596" t="inlineStr">
         <is>
@@ -69377,41 +69363,41 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E596" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I596" t="inlineStr"/>
       <c r="P596" t="inlineStr">
         <is>
-          <t>Verksmon, Jmt</t>
+          <t>Torvalla naturreservat, Torvalla naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q596" t="n">
-        <v>487060</v>
+        <v>486995</v>
       </c>
       <c r="R596" t="n">
-        <v>7004115</v>
+        <v>7003925</v>
       </c>
       <c r="S596" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T596" t="inlineStr">
         <is>
@@ -69455,22 +69441,22 @@
       <c r="AT596" t="inlineStr"/>
       <c r="AW596" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX596" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>119311630</v>
+        <v>119313079</v>
       </c>
       <c r="B597" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C597" t="inlineStr">
         <is>
@@ -69503,17 +69489,17 @@
       <c r="I597" t="inlineStr"/>
       <c r="P597" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q597" t="n">
-        <v>486944</v>
+        <v>486834</v>
       </c>
       <c r="R597" t="n">
-        <v>7003933</v>
+        <v>7004097</v>
       </c>
       <c r="S597" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T597" t="inlineStr">
         <is>
@@ -69557,22 +69543,22 @@
       <c r="AT597" t="inlineStr"/>
       <c r="AW597" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX597" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>119309241</v>
+        <v>119312982</v>
       </c>
       <c r="B598" t="n">
-        <v>57634</v>
+        <v>91895</v>
       </c>
       <c r="C598" t="inlineStr">
         <is>
@@ -69581,25 +69567,25 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E598" t="n">
-        <v>103021</v>
+        <v>4769</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I598" t="inlineStr"/>
@@ -69609,13 +69595,13 @@
         </is>
       </c>
       <c r="Q598" t="n">
-        <v>487066</v>
+        <v>486822</v>
       </c>
       <c r="R598" t="n">
-        <v>7004042</v>
+        <v>7004015</v>
       </c>
       <c r="S598" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T598" t="inlineStr">
         <is>
@@ -69671,10 +69657,10 @@
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>119312082</v>
+        <v>119311630</v>
       </c>
       <c r="B599" t="n">
-        <v>94769</v>
+        <v>78771</v>
       </c>
       <c r="C599" t="inlineStr">
         <is>
@@ -69683,25 +69669,25 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E599" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I599" t="inlineStr"/>
@@ -69711,13 +69697,13 @@
         </is>
       </c>
       <c r="Q599" t="n">
-        <v>486946</v>
+        <v>486944</v>
       </c>
       <c r="R599" t="n">
-        <v>7003956</v>
+        <v>7003933</v>
       </c>
       <c r="S599" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T599" t="inlineStr">
         <is>
@@ -69773,10 +69759,10 @@
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>119312923</v>
+        <v>119308870</v>
       </c>
       <c r="B600" t="n">
-        <v>57634</v>
+        <v>94771</v>
       </c>
       <c r="C600" t="inlineStr">
         <is>
@@ -69785,31 +69771,31 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E600" t="n">
-        <v>103021</v>
+        <v>2809</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I600" t="inlineStr"/>
       <c r="P600" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q600" t="n">
@@ -69819,7 +69805,7 @@
         <v>7004115</v>
       </c>
       <c r="S600" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T600" t="inlineStr">
         <is>
@@ -69875,10 +69861,10 @@
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>119309185</v>
+        <v>119312547</v>
       </c>
       <c r="B601" t="n">
-        <v>98368</v>
+        <v>97487</v>
       </c>
       <c r="C601" t="inlineStr">
         <is>
@@ -69887,41 +69873,41 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E601" t="n">
-        <v>220787</v>
+        <v>222741</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I601" t="inlineStr"/>
       <c r="P601" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q601" t="n">
-        <v>487054</v>
+        <v>487060</v>
       </c>
       <c r="R601" t="n">
-        <v>7004058</v>
+        <v>7004115</v>
       </c>
       <c r="S601" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T601" t="inlineStr">
         <is>
@@ -69965,22 +69951,22 @@
       <c r="AT601" t="inlineStr"/>
       <c r="AW601" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX601" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>119312547</v>
+        <v>119312412</v>
       </c>
       <c r="B602" t="n">
-        <v>97485</v>
+        <v>97383</v>
       </c>
       <c r="C602" t="inlineStr">
         <is>
@@ -69993,37 +69979,37 @@
         </is>
       </c>
       <c r="E602" t="n">
-        <v>222741</v>
+        <v>221063</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I602" t="inlineStr"/>
       <c r="P602" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q602" t="n">
-        <v>487060</v>
+        <v>486896</v>
       </c>
       <c r="R602" t="n">
-        <v>7004115</v>
+        <v>7003946</v>
       </c>
       <c r="S602" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T602" t="inlineStr">
         <is>
@@ -70067,22 +70053,22 @@
       <c r="AT602" t="inlineStr"/>
       <c r="AW602" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX602" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>119312982</v>
+        <v>119312398</v>
       </c>
       <c r="B603" t="n">
-        <v>91893</v>
+        <v>98370</v>
       </c>
       <c r="C603" t="inlineStr">
         <is>
@@ -70091,25 +70077,25 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E603" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I603" t="inlineStr"/>
@@ -70119,13 +70105,13 @@
         </is>
       </c>
       <c r="Q603" t="n">
-        <v>486822</v>
+        <v>486896</v>
       </c>
       <c r="R603" t="n">
-        <v>7004015</v>
+        <v>7003946</v>
       </c>
       <c r="S603" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T603" t="inlineStr">
         <is>
@@ -70181,10 +70167,10 @@
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>119313079</v>
+        <v>119312764</v>
       </c>
       <c r="B604" t="n">
-        <v>78769</v>
+        <v>97487</v>
       </c>
       <c r="C604" t="inlineStr">
         <is>
@@ -70193,25 +70179,25 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E604" t="n">
-        <v>6425</v>
+        <v>222741</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I604" t="inlineStr"/>
@@ -70221,10 +70207,10 @@
         </is>
       </c>
       <c r="Q604" t="n">
-        <v>486834</v>
+        <v>486807</v>
       </c>
       <c r="R604" t="n">
-        <v>7004097</v>
+        <v>7003950</v>
       </c>
       <c r="S604" t="n">
         <v>10</v>

--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -67612,10 +67612,10 @@
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>119311276</v>
+        <v>119312398</v>
       </c>
       <c r="B579" t="n">
-        <v>90957</v>
+        <v>98376</v>
       </c>
       <c r="C579" t="inlineStr">
         <is>
@@ -67624,41 +67624,41 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E579" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I579" t="inlineStr"/>
       <c r="P579" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q579" t="n">
-        <v>487004</v>
+        <v>486896</v>
       </c>
       <c r="R579" t="n">
-        <v>7003923</v>
+        <v>7003946</v>
       </c>
       <c r="S579" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T579" t="inlineStr">
         <is>
@@ -67714,10 +67714,10 @@
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>119312082</v>
+        <v>119308689</v>
       </c>
       <c r="B580" t="n">
-        <v>94771</v>
+        <v>98376</v>
       </c>
       <c r="C580" t="inlineStr">
         <is>
@@ -67726,41 +67726,55 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E580" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
-        </is>
-      </c>
-      <c r="I580" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P580" t="inlineStr">
         <is>
           <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q580" t="n">
-        <v>486946</v>
+        <v>487060</v>
       </c>
       <c r="R580" t="n">
-        <v>7003956</v>
+        <v>7004115</v>
       </c>
       <c r="S580" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T580" t="inlineStr">
         <is>
@@ -67816,10 +67830,10 @@
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>119312537</v>
+        <v>119313051</v>
       </c>
       <c r="B581" t="n">
-        <v>98370</v>
+        <v>78772</v>
       </c>
       <c r="C581" t="inlineStr">
         <is>
@@ -67828,41 +67842,41 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E581" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I581" t="inlineStr"/>
       <c r="P581" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q581" t="n">
-        <v>487060</v>
+        <v>486843</v>
       </c>
       <c r="R581" t="n">
-        <v>7004115</v>
+        <v>7004053</v>
       </c>
       <c r="S581" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T581" t="inlineStr">
         <is>
@@ -67906,22 +67920,22 @@
       <c r="AT581" t="inlineStr"/>
       <c r="AW581" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX581" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>119309185</v>
+        <v>119311193</v>
       </c>
       <c r="B582" t="n">
-        <v>98370</v>
+        <v>78772</v>
       </c>
       <c r="C582" t="inlineStr">
         <is>
@@ -67930,41 +67944,41 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E582" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I582" t="inlineStr"/>
       <c r="P582" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q582" t="n">
-        <v>487054</v>
+        <v>487004</v>
       </c>
       <c r="R582" t="n">
-        <v>7004058</v>
+        <v>7003923</v>
       </c>
       <c r="S582" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T582" t="inlineStr">
         <is>
@@ -68020,10 +68034,10 @@
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>119310718</v>
+        <v>119311723</v>
       </c>
       <c r="B583" t="n">
-        <v>78771</v>
+        <v>98376</v>
       </c>
       <c r="C583" t="inlineStr">
         <is>
@@ -68032,41 +68046,46 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E583" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P583" t="inlineStr">
         <is>
           <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q583" t="n">
-        <v>487060</v>
+        <v>486946</v>
       </c>
       <c r="R583" t="n">
-        <v>7004115</v>
+        <v>7003956</v>
       </c>
       <c r="S583" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T583" t="inlineStr">
         <is>
@@ -68122,10 +68141,10 @@
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>119309241</v>
+        <v>119308823</v>
       </c>
       <c r="B584" t="n">
-        <v>57634</v>
+        <v>91901</v>
       </c>
       <c r="C584" t="inlineStr">
         <is>
@@ -68134,41 +68153,41 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E584" t="n">
-        <v>103021</v>
+        <v>4769</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I584" t="inlineStr"/>
       <c r="P584" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q584" t="n">
-        <v>487066</v>
+        <v>487060</v>
       </c>
       <c r="R584" t="n">
-        <v>7004042</v>
+        <v>7004115</v>
       </c>
       <c r="S584" t="n">
-        <v>50</v>
+        <v>3</v>
       </c>
       <c r="T584" t="inlineStr">
         <is>
@@ -68212,12 +68231,12 @@
       <c r="AT584" t="inlineStr"/>
       <c r="AW584" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX584" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY584" t="inlineStr"/>
@@ -68326,10 +68345,10 @@
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>119312434</v>
+        <v>119313079</v>
       </c>
       <c r="B586" t="n">
-        <v>105461</v>
+        <v>78772</v>
       </c>
       <c r="C586" t="inlineStr">
         <is>
@@ -68338,25 +68357,25 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E586" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I586" t="inlineStr"/>
@@ -68366,10 +68385,10 @@
         </is>
       </c>
       <c r="Q586" t="n">
-        <v>486896</v>
+        <v>486834</v>
       </c>
       <c r="R586" t="n">
-        <v>7003946</v>
+        <v>7004097</v>
       </c>
       <c r="S586" t="n">
         <v>10</v>
@@ -68428,10 +68447,10 @@
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>119312223</v>
+        <v>119312764</v>
       </c>
       <c r="B587" t="n">
-        <v>97487</v>
+        <v>97492</v>
       </c>
       <c r="C587" t="inlineStr">
         <is>
@@ -68464,14 +68483,14 @@
       <c r="I587" t="inlineStr"/>
       <c r="P587" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q587" t="n">
-        <v>486946</v>
+        <v>486807</v>
       </c>
       <c r="R587" t="n">
-        <v>7003956</v>
+        <v>7003950</v>
       </c>
       <c r="S587" t="n">
         <v>10</v>
@@ -68518,22 +68537,22 @@
       <c r="AT587" t="inlineStr"/>
       <c r="AW587" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX587" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>119310979</v>
+        <v>119309475</v>
       </c>
       <c r="B588" t="n">
-        <v>91895</v>
+        <v>78772</v>
       </c>
       <c r="C588" t="inlineStr">
         <is>
@@ -68542,25 +68561,25 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E588" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I588" t="inlineStr"/>
@@ -68570,13 +68589,13 @@
         </is>
       </c>
       <c r="Q588" t="n">
-        <v>487043</v>
+        <v>487092</v>
       </c>
       <c r="R588" t="n">
-        <v>7003935</v>
+        <v>7004027</v>
       </c>
       <c r="S588" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T588" t="inlineStr">
         <is>
@@ -68632,10 +68651,10 @@
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>119308823</v>
+        <v>119311396</v>
       </c>
       <c r="B589" t="n">
-        <v>91895</v>
+        <v>98376</v>
       </c>
       <c r="C589" t="inlineStr">
         <is>
@@ -68644,41 +68663,41 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E589" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I589" t="inlineStr"/>
       <c r="P589" t="inlineStr">
         <is>
-          <t>Verksmon, Jmt</t>
+          <t>Torvalla naturreservat, Torvalla naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q589" t="n">
-        <v>487060</v>
+        <v>486995</v>
       </c>
       <c r="R589" t="n">
-        <v>7004115</v>
+        <v>7003925</v>
       </c>
       <c r="S589" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T589" t="inlineStr">
         <is>
@@ -68722,22 +68741,22 @@
       <c r="AT589" t="inlineStr"/>
       <c r="AW589" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX589" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>119313051</v>
+        <v>119309241</v>
       </c>
       <c r="B590" t="n">
-        <v>78771</v>
+        <v>57634</v>
       </c>
       <c r="C590" t="inlineStr">
         <is>
@@ -68750,21 +68769,21 @@
         </is>
       </c>
       <c r="E590" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I590" t="inlineStr"/>
@@ -68774,13 +68793,13 @@
         </is>
       </c>
       <c r="Q590" t="n">
-        <v>486843</v>
+        <v>487066</v>
       </c>
       <c r="R590" t="n">
-        <v>7004053</v>
+        <v>7004042</v>
       </c>
       <c r="S590" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T590" t="inlineStr">
         <is>
@@ -68836,10 +68855,10 @@
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>119309475</v>
+        <v>119311276</v>
       </c>
       <c r="B591" t="n">
-        <v>78771</v>
+        <v>90963</v>
       </c>
       <c r="C591" t="inlineStr">
         <is>
@@ -68852,21 +68871,21 @@
         </is>
       </c>
       <c r="E591" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I591" t="inlineStr"/>
@@ -68876,13 +68895,13 @@
         </is>
       </c>
       <c r="Q591" t="n">
-        <v>487092</v>
+        <v>487004</v>
       </c>
       <c r="R591" t="n">
-        <v>7004027</v>
+        <v>7003923</v>
       </c>
       <c r="S591" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T591" t="inlineStr">
         <is>
@@ -68938,10 +68957,10 @@
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>119311193</v>
+        <v>119312082</v>
       </c>
       <c r="B592" t="n">
-        <v>78771</v>
+        <v>94777</v>
       </c>
       <c r="C592" t="inlineStr">
         <is>
@@ -68950,25 +68969,25 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E592" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I592" t="inlineStr"/>
@@ -68978,13 +68997,13 @@
         </is>
       </c>
       <c r="Q592" t="n">
-        <v>487004</v>
+        <v>486946</v>
       </c>
       <c r="R592" t="n">
-        <v>7003923</v>
+        <v>7003956</v>
       </c>
       <c r="S592" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T592" t="inlineStr">
         <is>
@@ -69028,22 +69047,22 @@
       <c r="AT592" t="inlineStr"/>
       <c r="AW592" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX592" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>119311723</v>
+        <v>119312982</v>
       </c>
       <c r="B593" t="n">
-        <v>98370</v>
+        <v>91901</v>
       </c>
       <c r="C593" t="inlineStr">
         <is>
@@ -69052,46 +69071,41 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I593" t="inlineStr"/>
-      <c r="K593" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P593" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q593" t="n">
-        <v>486946</v>
+        <v>486822</v>
       </c>
       <c r="R593" t="n">
-        <v>7003956</v>
+        <v>7004015</v>
       </c>
       <c r="S593" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T593" t="inlineStr">
         <is>
@@ -69135,22 +69149,22 @@
       <c r="AT593" t="inlineStr"/>
       <c r="AW593" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX593" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>119311857</v>
+        <v>119312223</v>
       </c>
       <c r="B594" t="n">
-        <v>90957</v>
+        <v>97492</v>
       </c>
       <c r="C594" t="inlineStr">
         <is>
@@ -69159,41 +69173,41 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E594" t="n">
-        <v>1202</v>
+        <v>222741</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I594" t="inlineStr"/>
       <c r="P594" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q594" t="n">
-        <v>486943</v>
+        <v>486946</v>
       </c>
       <c r="R594" t="n">
-        <v>7003953</v>
+        <v>7003956</v>
       </c>
       <c r="S594" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T594" t="inlineStr">
         <is>
@@ -69237,22 +69251,22 @@
       <c r="AT594" t="inlineStr"/>
       <c r="AW594" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX594" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>119309504</v>
+        <v>119308870</v>
       </c>
       <c r="B595" t="n">
-        <v>98370</v>
+        <v>94777</v>
       </c>
       <c r="C595" t="inlineStr">
         <is>
@@ -69261,38 +69275,38 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E595" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I595" t="inlineStr"/>
       <c r="P595" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q595" t="n">
-        <v>487056</v>
+        <v>487060</v>
       </c>
       <c r="R595" t="n">
-        <v>7004063</v>
+        <v>7004115</v>
       </c>
       <c r="S595" t="n">
         <v>3</v>
@@ -69351,10 +69365,10 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>119311396</v>
+        <v>119312547</v>
       </c>
       <c r="B596" t="n">
-        <v>98370</v>
+        <v>97492</v>
       </c>
       <c r="C596" t="inlineStr">
         <is>
@@ -69363,41 +69377,41 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E596" t="n">
-        <v>220787</v>
+        <v>222741</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I596" t="inlineStr"/>
       <c r="P596" t="inlineStr">
         <is>
-          <t>Torvalla naturreservat, Torvalla naturreservat, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q596" t="n">
-        <v>486995</v>
+        <v>487060</v>
       </c>
       <c r="R596" t="n">
-        <v>7003925</v>
+        <v>7004115</v>
       </c>
       <c r="S596" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T596" t="inlineStr">
         <is>
@@ -69441,22 +69455,22 @@
       <c r="AT596" t="inlineStr"/>
       <c r="AW596" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX596" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>119313079</v>
+        <v>119310718</v>
       </c>
       <c r="B597" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C597" t="inlineStr">
         <is>
@@ -69489,17 +69503,17 @@
       <c r="I597" t="inlineStr"/>
       <c r="P597" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q597" t="n">
-        <v>486834</v>
+        <v>487060</v>
       </c>
       <c r="R597" t="n">
-        <v>7004097</v>
+        <v>7004115</v>
       </c>
       <c r="S597" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T597" t="inlineStr">
         <is>
@@ -69543,22 +69557,22 @@
       <c r="AT597" t="inlineStr"/>
       <c r="AW597" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX597" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>119312982</v>
+        <v>119312412</v>
       </c>
       <c r="B598" t="n">
-        <v>91895</v>
+        <v>97389</v>
       </c>
       <c r="C598" t="inlineStr">
         <is>
@@ -69571,21 +69585,21 @@
         </is>
       </c>
       <c r="E598" t="n">
-        <v>4769</v>
+        <v>221063</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I598" t="inlineStr"/>
@@ -69595,13 +69609,13 @@
         </is>
       </c>
       <c r="Q598" t="n">
-        <v>486822</v>
+        <v>486896</v>
       </c>
       <c r="R598" t="n">
-        <v>7004015</v>
+        <v>7003946</v>
       </c>
       <c r="S598" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T598" t="inlineStr">
         <is>
@@ -69657,10 +69671,10 @@
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>119311630</v>
+        <v>119312434</v>
       </c>
       <c r="B599" t="n">
-        <v>78771</v>
+        <v>105467</v>
       </c>
       <c r="C599" t="inlineStr">
         <is>
@@ -69669,41 +69683,41 @@
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E599" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I599" t="inlineStr"/>
       <c r="P599" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q599" t="n">
-        <v>486944</v>
+        <v>486896</v>
       </c>
       <c r="R599" t="n">
-        <v>7003933</v>
+        <v>7003946</v>
       </c>
       <c r="S599" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T599" t="inlineStr">
         <is>
@@ -69747,22 +69761,22 @@
       <c r="AT599" t="inlineStr"/>
       <c r="AW599" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX599" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>119308870</v>
+        <v>119311857</v>
       </c>
       <c r="B600" t="n">
-        <v>94771</v>
+        <v>90963</v>
       </c>
       <c r="C600" t="inlineStr">
         <is>
@@ -69771,41 +69785,41 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E600" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I600" t="inlineStr"/>
       <c r="P600" t="inlineStr">
         <is>
-          <t>Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q600" t="n">
-        <v>487060</v>
+        <v>486943</v>
       </c>
       <c r="R600" t="n">
-        <v>7004115</v>
+        <v>7003953</v>
       </c>
       <c r="S600" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T600" t="inlineStr">
         <is>
@@ -69849,22 +69863,22 @@
       <c r="AT600" t="inlineStr"/>
       <c r="AW600" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX600" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY600" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>119312547</v>
+        <v>119310979</v>
       </c>
       <c r="B601" t="n">
-        <v>97487</v>
+        <v>91901</v>
       </c>
       <c r="C601" t="inlineStr">
         <is>
@@ -69877,21 +69891,21 @@
         </is>
       </c>
       <c r="E601" t="n">
-        <v>222741</v>
+        <v>4769</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I601" t="inlineStr"/>
@@ -69901,13 +69915,13 @@
         </is>
       </c>
       <c r="Q601" t="n">
-        <v>487060</v>
+        <v>487043</v>
       </c>
       <c r="R601" t="n">
-        <v>7004115</v>
+        <v>7003935</v>
       </c>
       <c r="S601" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T601" t="inlineStr">
         <is>
@@ -69951,22 +69965,22 @@
       <c r="AT601" t="inlineStr"/>
       <c r="AW601" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX601" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>119312412</v>
+        <v>119309504</v>
       </c>
       <c r="B602" t="n">
-        <v>97383</v>
+        <v>98376</v>
       </c>
       <c r="C602" t="inlineStr">
         <is>
@@ -69975,41 +69989,41 @@
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E602" t="n">
-        <v>221063</v>
+        <v>220787</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I602" t="inlineStr"/>
       <c r="P602" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q602" t="n">
-        <v>486896</v>
+        <v>487056</v>
       </c>
       <c r="R602" t="n">
-        <v>7003946</v>
+        <v>7004063</v>
       </c>
       <c r="S602" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T602" t="inlineStr">
         <is>
@@ -70053,22 +70067,22 @@
       <c r="AT602" t="inlineStr"/>
       <c r="AW602" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX602" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>119312398</v>
+        <v>119309185</v>
       </c>
       <c r="B603" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C603" t="inlineStr">
         <is>
@@ -70105,10 +70119,10 @@
         </is>
       </c>
       <c r="Q603" t="n">
-        <v>486896</v>
+        <v>487054</v>
       </c>
       <c r="R603" t="n">
-        <v>7003946</v>
+        <v>7004058</v>
       </c>
       <c r="S603" t="n">
         <v>10</v>
@@ -70167,10 +70181,10 @@
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>119312764</v>
+        <v>119311630</v>
       </c>
       <c r="B604" t="n">
-        <v>97487</v>
+        <v>78772</v>
       </c>
       <c r="C604" t="inlineStr">
         <is>
@@ -70179,41 +70193,41 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E604" t="n">
-        <v>222741</v>
+        <v>6425</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I604" t="inlineStr"/>
       <c r="P604" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q604" t="n">
-        <v>486807</v>
+        <v>486944</v>
       </c>
       <c r="R604" t="n">
-        <v>7003950</v>
+        <v>7003933</v>
       </c>
       <c r="S604" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T604" t="inlineStr">
         <is>
@@ -70257,12 +70271,12 @@
       <c r="AT604" t="inlineStr"/>
       <c r="AW604" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX604" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY604" t="inlineStr"/>

--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -68957,10 +68957,10 @@
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>119312398</v>
+        <v>119309475</v>
       </c>
       <c r="B592" t="n">
-        <v>98379</v>
+        <v>78775</v>
       </c>
       <c r="C592" t="inlineStr">
         <is>
@@ -68969,38 +68969,38 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E592" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I592" t="inlineStr"/>
       <c r="P592" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q592" t="n">
-        <v>486896</v>
+        <v>487092</v>
       </c>
       <c r="R592" t="n">
-        <v>7003946</v>
+        <v>7004027</v>
       </c>
       <c r="S592" t="n">
         <v>10</v>
@@ -69059,10 +69059,10 @@
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>119309475</v>
+        <v>119312398</v>
       </c>
       <c r="B593" t="n">
-        <v>78775</v>
+        <v>98379</v>
       </c>
       <c r="C593" t="inlineStr">
         <is>
@@ -69071,38 +69071,38 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I593" t="inlineStr"/>
       <c r="P593" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q593" t="n">
-        <v>487092</v>
+        <v>486896</v>
       </c>
       <c r="R593" t="n">
-        <v>7004027</v>
+        <v>7003946</v>
       </c>
       <c r="S593" t="n">
         <v>10</v>

--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -67612,10 +67612,10 @@
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>119309241</v>
+        <v>119313051</v>
       </c>
       <c r="B579" t="n">
-        <v>57634</v>
+        <v>78781</v>
       </c>
       <c r="C579" t="inlineStr">
         <is>
@@ -67628,21 +67628,21 @@
         </is>
       </c>
       <c r="E579" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I579" t="inlineStr"/>
@@ -67652,13 +67652,13 @@
         </is>
       </c>
       <c r="Q579" t="n">
-        <v>487066</v>
+        <v>486843</v>
       </c>
       <c r="R579" t="n">
-        <v>7004042</v>
+        <v>7004053</v>
       </c>
       <c r="S579" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T579" t="inlineStr">
         <is>
@@ -67714,10 +67714,10 @@
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>119311396</v>
+        <v>119312531</v>
       </c>
       <c r="B580" t="n">
-        <v>98379</v>
+        <v>105487</v>
       </c>
       <c r="C580" t="inlineStr">
         <is>
@@ -67726,41 +67726,41 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E580" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I580" t="inlineStr"/>
       <c r="P580" t="inlineStr">
         <is>
-          <t>Torvalla naturreservat, Torvalla naturreservat, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q580" t="n">
-        <v>486995</v>
+        <v>486896</v>
       </c>
       <c r="R580" t="n">
-        <v>7003925</v>
+        <v>7003946</v>
       </c>
       <c r="S580" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T580" t="inlineStr">
         <is>
@@ -67816,10 +67816,10 @@
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>119311723</v>
+        <v>119308623</v>
       </c>
       <c r="B581" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C581" t="inlineStr">
         <is>
@@ -67849,7 +67849,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I581" t="inlineStr"/>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K581" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -67861,13 +67870,13 @@
         </is>
       </c>
       <c r="Q581" t="n">
-        <v>486946</v>
+        <v>487060</v>
       </c>
       <c r="R581" t="n">
-        <v>7003956</v>
+        <v>7004115</v>
       </c>
       <c r="S581" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T581" t="inlineStr">
         <is>
@@ -67923,10 +67932,10 @@
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>119312223</v>
+        <v>119311723</v>
       </c>
       <c r="B582" t="n">
-        <v>97495</v>
+        <v>98396</v>
       </c>
       <c r="C582" t="inlineStr">
         <is>
@@ -67935,28 +67944,33 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E582" t="n">
-        <v>222741</v>
+        <v>220787</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P582" t="inlineStr">
         <is>
           <t>Verksmon, Verksmon, Jmt</t>
@@ -67969,7 +67983,7 @@
         <v>7003956</v>
       </c>
       <c r="S582" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T582" t="inlineStr">
         <is>
@@ -68025,10 +68039,10 @@
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>119312412</v>
+        <v>119309475</v>
       </c>
       <c r="B583" t="n">
-        <v>97392</v>
+        <v>78781</v>
       </c>
       <c r="C583" t="inlineStr">
         <is>
@@ -68037,38 +68051,38 @@
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E583" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I583" t="inlineStr"/>
       <c r="P583" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q583" t="n">
-        <v>486896</v>
+        <v>487092</v>
       </c>
       <c r="R583" t="n">
-        <v>7003946</v>
+        <v>7004027</v>
       </c>
       <c r="S583" t="n">
         <v>10</v>
@@ -68127,10 +68141,10 @@
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>119311630</v>
+        <v>119313079</v>
       </c>
       <c r="B584" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C584" t="inlineStr">
         <is>
@@ -68163,17 +68177,17 @@
       <c r="I584" t="inlineStr"/>
       <c r="P584" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q584" t="n">
-        <v>486944</v>
+        <v>486834</v>
       </c>
       <c r="R584" t="n">
-        <v>7003933</v>
+        <v>7004097</v>
       </c>
       <c r="S584" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T584" t="inlineStr">
         <is>
@@ -68217,22 +68231,22 @@
       <c r="AT584" t="inlineStr"/>
       <c r="AW584" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX584" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY584" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>119308870</v>
+        <v>119311276</v>
       </c>
       <c r="B585" t="n">
-        <v>94780</v>
+        <v>90983</v>
       </c>
       <c r="C585" t="inlineStr">
         <is>
@@ -68241,41 +68255,41 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E585" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I585" t="inlineStr"/>
       <c r="P585" t="inlineStr">
         <is>
-          <t>Verksmon, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q585" t="n">
-        <v>487060</v>
+        <v>487004</v>
       </c>
       <c r="R585" t="n">
-        <v>7004115</v>
+        <v>7003923</v>
       </c>
       <c r="S585" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T585" t="inlineStr">
         <is>
@@ -68319,22 +68333,22 @@
       <c r="AT585" t="inlineStr"/>
       <c r="AW585" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX585" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>119312531</v>
+        <v>119310718</v>
       </c>
       <c r="B586" t="n">
-        <v>105470</v>
+        <v>78781</v>
       </c>
       <c r="C586" t="inlineStr">
         <is>
@@ -68343,41 +68357,41 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E586" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I586" t="inlineStr"/>
       <c r="P586" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q586" t="n">
-        <v>486896</v>
+        <v>487060</v>
       </c>
       <c r="R586" t="n">
-        <v>7003946</v>
+        <v>7004115</v>
       </c>
       <c r="S586" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T586" t="inlineStr">
         <is>
@@ -68421,22 +68435,22 @@
       <c r="AT586" t="inlineStr"/>
       <c r="AW586" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX586" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>119312082</v>
+        <v>119311857</v>
       </c>
       <c r="B587" t="n">
-        <v>94780</v>
+        <v>90983</v>
       </c>
       <c r="C587" t="inlineStr">
         <is>
@@ -68445,41 +68459,41 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E587" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I587" t="inlineStr"/>
       <c r="P587" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q587" t="n">
-        <v>486946</v>
+        <v>486943</v>
       </c>
       <c r="R587" t="n">
-        <v>7003956</v>
+        <v>7003953</v>
       </c>
       <c r="S587" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T587" t="inlineStr">
         <is>
@@ -68523,22 +68537,22 @@
       <c r="AT587" t="inlineStr"/>
       <c r="AW587" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX587" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>119313051</v>
+        <v>119312398</v>
       </c>
       <c r="B588" t="n">
-        <v>78775</v>
+        <v>98396</v>
       </c>
       <c r="C588" t="inlineStr">
         <is>
@@ -68547,25 +68561,25 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E588" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I588" t="inlineStr"/>
@@ -68575,10 +68589,10 @@
         </is>
       </c>
       <c r="Q588" t="n">
-        <v>486843</v>
+        <v>486896</v>
       </c>
       <c r="R588" t="n">
-        <v>7004053</v>
+        <v>7003946</v>
       </c>
       <c r="S588" t="n">
         <v>10</v>
@@ -68637,10 +68651,10 @@
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>119311857</v>
+        <v>119312412</v>
       </c>
       <c r="B589" t="n">
-        <v>90966</v>
+        <v>97409</v>
       </c>
       <c r="C589" t="inlineStr">
         <is>
@@ -68649,25 +68663,25 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E589" t="n">
-        <v>1202</v>
+        <v>221063</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I589" t="inlineStr"/>
@@ -68677,13 +68691,13 @@
         </is>
       </c>
       <c r="Q589" t="n">
-        <v>486943</v>
+        <v>486896</v>
       </c>
       <c r="R589" t="n">
-        <v>7003953</v>
+        <v>7003946</v>
       </c>
       <c r="S589" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T589" t="inlineStr">
         <is>
@@ -68739,10 +68753,10 @@
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>119312547</v>
+        <v>119311630</v>
       </c>
       <c r="B590" t="n">
-        <v>97495</v>
+        <v>78781</v>
       </c>
       <c r="C590" t="inlineStr">
         <is>
@@ -68751,25 +68765,25 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E590" t="n">
-        <v>222741</v>
+        <v>6425</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I590" t="inlineStr"/>
@@ -68779,13 +68793,13 @@
         </is>
       </c>
       <c r="Q590" t="n">
-        <v>487060</v>
+        <v>486944</v>
       </c>
       <c r="R590" t="n">
-        <v>7004115</v>
+        <v>7003933</v>
       </c>
       <c r="S590" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T590" t="inlineStr">
         <is>
@@ -68841,10 +68855,10 @@
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>119308623</v>
+        <v>119309495</v>
       </c>
       <c r="B591" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C591" t="inlineStr">
         <is>
@@ -68874,31 +68888,22 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I591" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I591" t="inlineStr"/>
       <c r="J591" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P591" t="inlineStr">
         <is>
           <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q591" t="n">
-        <v>487060</v>
+        <v>487056</v>
       </c>
       <c r="R591" t="n">
-        <v>7004115</v>
+        <v>7004063</v>
       </c>
       <c r="S591" t="n">
         <v>3</v>
@@ -68957,10 +68962,10 @@
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>119309475</v>
+        <v>119312547</v>
       </c>
       <c r="B592" t="n">
-        <v>78775</v>
+        <v>97512</v>
       </c>
       <c r="C592" t="inlineStr">
         <is>
@@ -68969,25 +68974,25 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E592" t="n">
-        <v>6425</v>
+        <v>222741</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I592" t="inlineStr"/>
@@ -68997,13 +69002,13 @@
         </is>
       </c>
       <c r="Q592" t="n">
-        <v>487092</v>
+        <v>487060</v>
       </c>
       <c r="R592" t="n">
-        <v>7004027</v>
+        <v>7004115</v>
       </c>
       <c r="S592" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T592" t="inlineStr">
         <is>
@@ -69047,22 +69052,22 @@
       <c r="AT592" t="inlineStr"/>
       <c r="AW592" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX592" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>119312398</v>
+        <v>119310979</v>
       </c>
       <c r="B593" t="n">
-        <v>98379</v>
+        <v>91921</v>
       </c>
       <c r="C593" t="inlineStr">
         <is>
@@ -69071,41 +69076,41 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I593" t="inlineStr"/>
       <c r="P593" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q593" t="n">
-        <v>486896</v>
+        <v>487043</v>
       </c>
       <c r="R593" t="n">
-        <v>7003946</v>
+        <v>7003935</v>
       </c>
       <c r="S593" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T593" t="inlineStr">
         <is>
@@ -69161,10 +69166,10 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>119309495</v>
+        <v>119312923</v>
       </c>
       <c r="B594" t="n">
-        <v>98379</v>
+        <v>57640</v>
       </c>
       <c r="C594" t="inlineStr">
         <is>
@@ -69173,46 +69178,41 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E594" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I594" t="inlineStr"/>
-      <c r="J594" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P594" t="inlineStr">
         <is>
           <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q594" t="n">
-        <v>487056</v>
+        <v>487060</v>
       </c>
       <c r="R594" t="n">
-        <v>7004063</v>
+        <v>7004115</v>
       </c>
       <c r="S594" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T594" t="inlineStr">
         <is>
@@ -69268,10 +69268,10 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>119312982</v>
+        <v>119312764</v>
       </c>
       <c r="B595" t="n">
-        <v>91904</v>
+        <v>97512</v>
       </c>
       <c r="C595" t="inlineStr">
         <is>
@@ -69284,21 +69284,21 @@
         </is>
       </c>
       <c r="E595" t="n">
-        <v>4769</v>
+        <v>222741</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I595" t="inlineStr"/>
@@ -69308,13 +69308,13 @@
         </is>
       </c>
       <c r="Q595" t="n">
-        <v>486822</v>
+        <v>486807</v>
       </c>
       <c r="R595" t="n">
-        <v>7004015</v>
+        <v>7003950</v>
       </c>
       <c r="S595" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T595" t="inlineStr">
         <is>
@@ -69370,10 +69370,10 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>119313079</v>
+        <v>119312982</v>
       </c>
       <c r="B596" t="n">
-        <v>78775</v>
+        <v>91921</v>
       </c>
       <c r="C596" t="inlineStr">
         <is>
@@ -69382,25 +69382,25 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E596" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I596" t="inlineStr"/>
@@ -69410,13 +69410,13 @@
         </is>
       </c>
       <c r="Q596" t="n">
-        <v>486834</v>
+        <v>486822</v>
       </c>
       <c r="R596" t="n">
-        <v>7004097</v>
+        <v>7004015</v>
       </c>
       <c r="S596" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T596" t="inlineStr">
         <is>
@@ -69472,10 +69472,10 @@
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>119309185</v>
+        <v>119308870</v>
       </c>
       <c r="B597" t="n">
-        <v>98379</v>
+        <v>94797</v>
       </c>
       <c r="C597" t="inlineStr">
         <is>
@@ -69484,41 +69484,41 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E597" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I597" t="inlineStr"/>
       <c r="P597" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q597" t="n">
-        <v>487054</v>
+        <v>487060</v>
       </c>
       <c r="R597" t="n">
-        <v>7004058</v>
+        <v>7004115</v>
       </c>
       <c r="S597" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T597" t="inlineStr">
         <is>
@@ -69562,22 +69562,22 @@
       <c r="AT597" t="inlineStr"/>
       <c r="AW597" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX597" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>119312764</v>
+        <v>119308823</v>
       </c>
       <c r="B598" t="n">
-        <v>97495</v>
+        <v>91921</v>
       </c>
       <c r="C598" t="inlineStr">
         <is>
@@ -69590,37 +69590,37 @@
         </is>
       </c>
       <c r="E598" t="n">
-        <v>222741</v>
+        <v>4769</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I598" t="inlineStr"/>
       <c r="P598" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q598" t="n">
-        <v>486807</v>
+        <v>487060</v>
       </c>
       <c r="R598" t="n">
-        <v>7003950</v>
+        <v>7004115</v>
       </c>
       <c r="S598" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T598" t="inlineStr">
         <is>
@@ -69664,22 +69664,22 @@
       <c r="AT598" t="inlineStr"/>
       <c r="AW598" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX598" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY598" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>119310718</v>
+        <v>119309241</v>
       </c>
       <c r="B599" t="n">
-        <v>78775</v>
+        <v>57640</v>
       </c>
       <c r="C599" t="inlineStr">
         <is>
@@ -69692,37 +69692,37 @@
         </is>
       </c>
       <c r="E599" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I599" t="inlineStr"/>
       <c r="P599" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q599" t="n">
-        <v>487060</v>
+        <v>487066</v>
       </c>
       <c r="R599" t="n">
-        <v>7004115</v>
+        <v>7004042</v>
       </c>
       <c r="S599" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T599" t="inlineStr">
         <is>
@@ -69766,22 +69766,22 @@
       <c r="AT599" t="inlineStr"/>
       <c r="AW599" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX599" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY599" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>119310979</v>
+        <v>119309185</v>
       </c>
       <c r="B600" t="n">
-        <v>91904</v>
+        <v>98396</v>
       </c>
       <c r="C600" t="inlineStr">
         <is>
@@ -69790,41 +69790,41 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E600" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I600" t="inlineStr"/>
       <c r="P600" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q600" t="n">
-        <v>487043</v>
+        <v>487054</v>
       </c>
       <c r="R600" t="n">
-        <v>7003935</v>
+        <v>7004058</v>
       </c>
       <c r="S600" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T600" t="inlineStr">
         <is>
@@ -69880,10 +69880,10 @@
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>119311276</v>
+        <v>119312082</v>
       </c>
       <c r="B601" t="n">
-        <v>90966</v>
+        <v>94797</v>
       </c>
       <c r="C601" t="inlineStr">
         <is>
@@ -69892,25 +69892,25 @@
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E601" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I601" t="inlineStr"/>
@@ -69920,13 +69920,13 @@
         </is>
       </c>
       <c r="Q601" t="n">
-        <v>487004</v>
+        <v>486946</v>
       </c>
       <c r="R601" t="n">
-        <v>7003923</v>
+        <v>7003956</v>
       </c>
       <c r="S601" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T601" t="inlineStr">
         <is>
@@ -69970,22 +69970,22 @@
       <c r="AT601" t="inlineStr"/>
       <c r="AW601" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX601" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>119312923</v>
+        <v>119311193</v>
       </c>
       <c r="B602" t="n">
-        <v>57634</v>
+        <v>78781</v>
       </c>
       <c r="C602" t="inlineStr">
         <is>
@@ -69998,21 +69998,21 @@
         </is>
       </c>
       <c r="E602" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G602" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I602" t="inlineStr"/>
@@ -70022,13 +70022,13 @@
         </is>
       </c>
       <c r="Q602" t="n">
-        <v>487060</v>
+        <v>487004</v>
       </c>
       <c r="R602" t="n">
-        <v>7004115</v>
+        <v>7003923</v>
       </c>
       <c r="S602" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T602" t="inlineStr">
         <is>
@@ -70072,22 +70072,22 @@
       <c r="AT602" t="inlineStr"/>
       <c r="AW602" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX602" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>119308823</v>
+        <v>119312223</v>
       </c>
       <c r="B603" t="n">
-        <v>91904</v>
+        <v>97512</v>
       </c>
       <c r="C603" t="inlineStr">
         <is>
@@ -70100,37 +70100,37 @@
         </is>
       </c>
       <c r="E603" t="n">
-        <v>4769</v>
+        <v>222741</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I603" t="inlineStr"/>
       <c r="P603" t="inlineStr">
         <is>
-          <t>Verksmon, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q603" t="n">
-        <v>487060</v>
+        <v>486946</v>
       </c>
       <c r="R603" t="n">
-        <v>7004115</v>
+        <v>7003956</v>
       </c>
       <c r="S603" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T603" t="inlineStr">
         <is>
@@ -70186,10 +70186,10 @@
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>119311193</v>
+        <v>119311396</v>
       </c>
       <c r="B604" t="n">
-        <v>78775</v>
+        <v>98396</v>
       </c>
       <c r="C604" t="inlineStr">
         <is>
@@ -70198,38 +70198,38 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E604" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I604" t="inlineStr"/>
       <c r="P604" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Torvalla naturreservat, Torvalla naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q604" t="n">
-        <v>487004</v>
+        <v>486995</v>
       </c>
       <c r="R604" t="n">
-        <v>7003923</v>
+        <v>7003925</v>
       </c>
       <c r="S604" t="n">
         <v>20</v>

--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -68345,10 +68345,10 @@
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>119310718</v>
+        <v>119311857</v>
       </c>
       <c r="B586" t="n">
-        <v>78781</v>
+        <v>90983</v>
       </c>
       <c r="C586" t="inlineStr">
         <is>
@@ -68361,37 +68361,37 @@
         </is>
       </c>
       <c r="E586" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I586" t="inlineStr"/>
       <c r="P586" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q586" t="n">
-        <v>487060</v>
+        <v>486943</v>
       </c>
       <c r="R586" t="n">
-        <v>7004115</v>
+        <v>7003953</v>
       </c>
       <c r="S586" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T586" t="inlineStr">
         <is>
@@ -68435,22 +68435,22 @@
       <c r="AT586" t="inlineStr"/>
       <c r="AW586" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX586" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>119311857</v>
+        <v>119310718</v>
       </c>
       <c r="B587" t="n">
-        <v>90983</v>
+        <v>78781</v>
       </c>
       <c r="C587" t="inlineStr">
         <is>
@@ -68463,37 +68463,37 @@
         </is>
       </c>
       <c r="E587" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I587" t="inlineStr"/>
       <c r="P587" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q587" t="n">
-        <v>486943</v>
+        <v>487060</v>
       </c>
       <c r="R587" t="n">
-        <v>7003953</v>
+        <v>7004115</v>
       </c>
       <c r="S587" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T587" t="inlineStr">
         <is>
@@ -68537,12 +68537,12 @@
       <c r="AT587" t="inlineStr"/>
       <c r="AW587" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX587" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY587" t="inlineStr"/>

--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -68855,10 +68855,10 @@
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>119309495</v>
+        <v>119312547</v>
       </c>
       <c r="B591" t="n">
-        <v>98396</v>
+        <v>97512</v>
       </c>
       <c r="C591" t="inlineStr">
         <is>
@@ -68867,43 +68867,38 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E591" t="n">
-        <v>220787</v>
+        <v>222741</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I591" t="inlineStr"/>
-      <c r="J591" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P591" t="inlineStr">
         <is>
           <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q591" t="n">
-        <v>487056</v>
+        <v>487060</v>
       </c>
       <c r="R591" t="n">
-        <v>7004063</v>
+        <v>7004115</v>
       </c>
       <c r="S591" t="n">
         <v>3</v>
@@ -68962,10 +68957,10 @@
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>119312547</v>
+        <v>119309495</v>
       </c>
       <c r="B592" t="n">
-        <v>97512</v>
+        <v>98396</v>
       </c>
       <c r="C592" t="inlineStr">
         <is>
@@ -68974,38 +68969,43 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E592" t="n">
-        <v>222741</v>
+        <v>220787</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I592" t="inlineStr"/>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P592" t="inlineStr">
         <is>
           <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q592" t="n">
-        <v>487060</v>
+        <v>487056</v>
       </c>
       <c r="R592" t="n">
-        <v>7004115</v>
+        <v>7004063</v>
       </c>
       <c r="S592" t="n">
         <v>3</v>
@@ -69064,10 +69064,10 @@
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>119310979</v>
+        <v>119312764</v>
       </c>
       <c r="B593" t="n">
-        <v>91921</v>
+        <v>97512</v>
       </c>
       <c r="C593" t="inlineStr">
         <is>
@@ -69080,37 +69080,37 @@
         </is>
       </c>
       <c r="E593" t="n">
-        <v>4769</v>
+        <v>222741</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I593" t="inlineStr"/>
       <c r="P593" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q593" t="n">
-        <v>487043</v>
+        <v>486807</v>
       </c>
       <c r="R593" t="n">
-        <v>7003935</v>
+        <v>7003950</v>
       </c>
       <c r="S593" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T593" t="inlineStr">
         <is>
@@ -69166,10 +69166,10 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>119312923</v>
+        <v>119310979</v>
       </c>
       <c r="B594" t="n">
-        <v>57640</v>
+        <v>91921</v>
       </c>
       <c r="C594" t="inlineStr">
         <is>
@@ -69178,25 +69178,25 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E594" t="n">
-        <v>103021</v>
+        <v>4769</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I594" t="inlineStr"/>
@@ -69206,13 +69206,13 @@
         </is>
       </c>
       <c r="Q594" t="n">
-        <v>487060</v>
+        <v>487043</v>
       </c>
       <c r="R594" t="n">
-        <v>7004115</v>
+        <v>7003935</v>
       </c>
       <c r="S594" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T594" t="inlineStr">
         <is>
@@ -69256,22 +69256,22 @@
       <c r="AT594" t="inlineStr"/>
       <c r="AW594" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX594" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY594" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>119312764</v>
+        <v>119312923</v>
       </c>
       <c r="B595" t="n">
-        <v>97512</v>
+        <v>57640</v>
       </c>
       <c r="C595" t="inlineStr">
         <is>
@@ -69280,38 +69280,38 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E595" t="n">
-        <v>222741</v>
+        <v>103021</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I595" t="inlineStr"/>
       <c r="P595" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q595" t="n">
-        <v>486807</v>
+        <v>487060</v>
       </c>
       <c r="R595" t="n">
-        <v>7003950</v>
+        <v>7004115</v>
       </c>
       <c r="S595" t="n">
         <v>10</v>
@@ -69358,12 +69358,12 @@
       <c r="AT595" t="inlineStr"/>
       <c r="AW595" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX595" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY595" t="inlineStr"/>

--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -68345,10 +68345,10 @@
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>119311857</v>
+        <v>119310718</v>
       </c>
       <c r="B586" t="n">
-        <v>90983</v>
+        <v>78781</v>
       </c>
       <c r="C586" t="inlineStr">
         <is>
@@ -68361,37 +68361,37 @@
         </is>
       </c>
       <c r="E586" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I586" t="inlineStr"/>
       <c r="P586" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q586" t="n">
-        <v>486943</v>
+        <v>487060</v>
       </c>
       <c r="R586" t="n">
-        <v>7003953</v>
+        <v>7004115</v>
       </c>
       <c r="S586" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T586" t="inlineStr">
         <is>
@@ -68435,22 +68435,22 @@
       <c r="AT586" t="inlineStr"/>
       <c r="AW586" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX586" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>119310718</v>
+        <v>119311857</v>
       </c>
       <c r="B587" t="n">
-        <v>78781</v>
+        <v>90983</v>
       </c>
       <c r="C587" t="inlineStr">
         <is>
@@ -68463,37 +68463,37 @@
         </is>
       </c>
       <c r="E587" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I587" t="inlineStr"/>
       <c r="P587" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q587" t="n">
-        <v>487060</v>
+        <v>486943</v>
       </c>
       <c r="R587" t="n">
-        <v>7004115</v>
+        <v>7003953</v>
       </c>
       <c r="S587" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T587" t="inlineStr">
         <is>
@@ -68537,12 +68537,12 @@
       <c r="AT587" t="inlineStr"/>
       <c r="AW587" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX587" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY587" t="inlineStr"/>
@@ -68855,10 +68855,10 @@
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>119312547</v>
+        <v>119309495</v>
       </c>
       <c r="B591" t="n">
-        <v>97512</v>
+        <v>98396</v>
       </c>
       <c r="C591" t="inlineStr">
         <is>
@@ -68867,38 +68867,43 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E591" t="n">
-        <v>222741</v>
+        <v>220787</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I591" t="inlineStr"/>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P591" t="inlineStr">
         <is>
           <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q591" t="n">
-        <v>487060</v>
+        <v>487056</v>
       </c>
       <c r="R591" t="n">
-        <v>7004115</v>
+        <v>7004063</v>
       </c>
       <c r="S591" t="n">
         <v>3</v>
@@ -68957,10 +68962,10 @@
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>119309495</v>
+        <v>119312547</v>
       </c>
       <c r="B592" t="n">
-        <v>98396</v>
+        <v>97512</v>
       </c>
       <c r="C592" t="inlineStr">
         <is>
@@ -68969,43 +68974,38 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E592" t="n">
-        <v>220787</v>
+        <v>222741</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I592" t="inlineStr"/>
-      <c r="J592" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P592" t="inlineStr">
         <is>
           <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q592" t="n">
-        <v>487056</v>
+        <v>487060</v>
       </c>
       <c r="R592" t="n">
-        <v>7004063</v>
+        <v>7004115</v>
       </c>
       <c r="S592" t="n">
         <v>3</v>

--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -67612,10 +67612,10 @@
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>119313051</v>
+        <v>119312223</v>
       </c>
       <c r="B579" t="n">
-        <v>78781</v>
+        <v>97529</v>
       </c>
       <c r="C579" t="inlineStr">
         <is>
@@ -67624,38 +67624,38 @@
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E579" t="n">
-        <v>6425</v>
+        <v>222741</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I579" t="inlineStr"/>
       <c r="P579" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q579" t="n">
-        <v>486843</v>
+        <v>486946</v>
       </c>
       <c r="R579" t="n">
-        <v>7004053</v>
+        <v>7003956</v>
       </c>
       <c r="S579" t="n">
         <v>10</v>
@@ -67702,22 +67702,22 @@
       <c r="AT579" t="inlineStr"/>
       <c r="AW579" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX579" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY579" t="inlineStr"/>
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>119312531</v>
+        <v>119312082</v>
       </c>
       <c r="B580" t="n">
-        <v>105487</v>
+        <v>94803</v>
       </c>
       <c r="C580" t="inlineStr">
         <is>
@@ -67730,34 +67730,34 @@
         </is>
       </c>
       <c r="E580" t="n">
-        <v>221725</v>
+        <v>2809</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I580" t="inlineStr"/>
       <c r="P580" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q580" t="n">
-        <v>486896</v>
+        <v>486946</v>
       </c>
       <c r="R580" t="n">
-        <v>7003946</v>
+        <v>7003956</v>
       </c>
       <c r="S580" t="n">
         <v>10</v>
@@ -67804,22 +67804,22 @@
       <c r="AT580" t="inlineStr"/>
       <c r="AW580" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX580" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY580" t="inlineStr"/>
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>119308623</v>
+        <v>119313051</v>
       </c>
       <c r="B581" t="n">
-        <v>98396</v>
+        <v>78786</v>
       </c>
       <c r="C581" t="inlineStr">
         <is>
@@ -67828,55 +67828,41 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E581" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I581" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J581" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K581" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr"/>
       <c r="P581" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q581" t="n">
-        <v>487060</v>
+        <v>486843</v>
       </c>
       <c r="R581" t="n">
-        <v>7004115</v>
+        <v>7004053</v>
       </c>
       <c r="S581" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T581" t="inlineStr">
         <is>
@@ -67920,22 +67906,22 @@
       <c r="AT581" t="inlineStr"/>
       <c r="AW581" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX581" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY581" t="inlineStr"/>
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>119311723</v>
+        <v>119310718</v>
       </c>
       <c r="B582" t="n">
-        <v>98396</v>
+        <v>78786</v>
       </c>
       <c r="C582" t="inlineStr">
         <is>
@@ -67944,46 +67930,41 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E582" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I582" t="inlineStr"/>
-      <c r="K582" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P582" t="inlineStr">
         <is>
           <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q582" t="n">
-        <v>486946</v>
+        <v>487060</v>
       </c>
       <c r="R582" t="n">
-        <v>7003956</v>
+        <v>7004115</v>
       </c>
       <c r="S582" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T582" t="inlineStr">
         <is>
@@ -68039,10 +68020,10 @@
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>119309475</v>
+        <v>119311857</v>
       </c>
       <c r="B583" t="n">
-        <v>78781</v>
+        <v>90988</v>
       </c>
       <c r="C583" t="inlineStr">
         <is>
@@ -68055,37 +68036,37 @@
         </is>
       </c>
       <c r="E583" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I583" t="inlineStr"/>
       <c r="P583" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q583" t="n">
-        <v>487092</v>
+        <v>486943</v>
       </c>
       <c r="R583" t="n">
-        <v>7004027</v>
+        <v>7003953</v>
       </c>
       <c r="S583" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T583" t="inlineStr">
         <is>
@@ -68144,7 +68125,7 @@
         <v>119313079</v>
       </c>
       <c r="B584" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C584" t="inlineStr">
         <is>
@@ -68243,10 +68224,10 @@
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>119311276</v>
+        <v>119312434</v>
       </c>
       <c r="B585" t="n">
-        <v>90983</v>
+        <v>105503</v>
       </c>
       <c r="C585" t="inlineStr">
         <is>
@@ -68255,41 +68236,41 @@
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E585" t="n">
-        <v>1202</v>
+        <v>221725</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I585" t="inlineStr"/>
       <c r="P585" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q585" t="n">
-        <v>487004</v>
+        <v>486896</v>
       </c>
       <c r="R585" t="n">
-        <v>7003923</v>
+        <v>7003946</v>
       </c>
       <c r="S585" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T585" t="inlineStr">
         <is>
@@ -68345,10 +68326,10 @@
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>119310718</v>
+        <v>119312982</v>
       </c>
       <c r="B586" t="n">
-        <v>78781</v>
+        <v>91926</v>
       </c>
       <c r="C586" t="inlineStr">
         <is>
@@ -68357,41 +68338,41 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E586" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I586" t="inlineStr"/>
       <c r="P586" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q586" t="n">
-        <v>487060</v>
+        <v>486822</v>
       </c>
       <c r="R586" t="n">
-        <v>7004115</v>
+        <v>7004015</v>
       </c>
       <c r="S586" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T586" t="inlineStr">
         <is>
@@ -68435,22 +68416,22 @@
       <c r="AT586" t="inlineStr"/>
       <c r="AW586" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX586" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY586" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>119311857</v>
+        <v>119312412</v>
       </c>
       <c r="B587" t="n">
-        <v>90983</v>
+        <v>97426</v>
       </c>
       <c r="C587" t="inlineStr">
         <is>
@@ -68459,25 +68440,25 @@
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E587" t="n">
-        <v>1202</v>
+        <v>221063</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I587" t="inlineStr"/>
@@ -68487,13 +68468,13 @@
         </is>
       </c>
       <c r="Q587" t="n">
-        <v>486943</v>
+        <v>486896</v>
       </c>
       <c r="R587" t="n">
-        <v>7003953</v>
+        <v>7003946</v>
       </c>
       <c r="S587" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T587" t="inlineStr">
         <is>
@@ -68549,10 +68530,10 @@
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>119312398</v>
+        <v>119311723</v>
       </c>
       <c r="B588" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C588" t="inlineStr">
         <is>
@@ -68583,19 +68564,24 @@
         </is>
       </c>
       <c r="I588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P588" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q588" t="n">
-        <v>486896</v>
+        <v>486946</v>
       </c>
       <c r="R588" t="n">
-        <v>7003946</v>
+        <v>7003956</v>
       </c>
       <c r="S588" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T588" t="inlineStr">
         <is>
@@ -68639,22 +68625,22 @@
       <c r="AT588" t="inlineStr"/>
       <c r="AW588" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX588" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>119312412</v>
+        <v>119309185</v>
       </c>
       <c r="B589" t="n">
-        <v>97409</v>
+        <v>98502</v>
       </c>
       <c r="C589" t="inlineStr">
         <is>
@@ -68663,25 +68649,25 @@
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E589" t="n">
-        <v>221063</v>
+        <v>220787</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I589" t="inlineStr"/>
@@ -68691,10 +68677,10 @@
         </is>
       </c>
       <c r="Q589" t="n">
-        <v>486896</v>
+        <v>487054</v>
       </c>
       <c r="R589" t="n">
-        <v>7003946</v>
+        <v>7004058</v>
       </c>
       <c r="S589" t="n">
         <v>10</v>
@@ -68753,10 +68739,10 @@
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>119311630</v>
+        <v>119308823</v>
       </c>
       <c r="B590" t="n">
-        <v>78781</v>
+        <v>91926</v>
       </c>
       <c r="C590" t="inlineStr">
         <is>
@@ -68765,41 +68751,41 @@
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E590" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I590" t="inlineStr"/>
       <c r="P590" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q590" t="n">
-        <v>486944</v>
+        <v>487060</v>
       </c>
       <c r="R590" t="n">
-        <v>7003933</v>
+        <v>7004115</v>
       </c>
       <c r="S590" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T590" t="inlineStr">
         <is>
@@ -68855,10 +68841,10 @@
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>119309495</v>
+        <v>119309241</v>
       </c>
       <c r="B591" t="n">
-        <v>98396</v>
+        <v>57643</v>
       </c>
       <c r="C591" t="inlineStr">
         <is>
@@ -68867,46 +68853,41 @@
       </c>
       <c r="D591" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E591" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I591" t="inlineStr"/>
-      <c r="J591" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P591" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q591" t="n">
-        <v>487056</v>
+        <v>487066</v>
       </c>
       <c r="R591" t="n">
-        <v>7004063</v>
+        <v>7004042</v>
       </c>
       <c r="S591" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="T591" t="inlineStr">
         <is>
@@ -68950,22 +68931,22 @@
       <c r="AT591" t="inlineStr"/>
       <c r="AW591" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX591" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY591" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>119312547</v>
+        <v>119311630</v>
       </c>
       <c r="B592" t="n">
-        <v>97512</v>
+        <v>78786</v>
       </c>
       <c r="C592" t="inlineStr">
         <is>
@@ -68974,25 +68955,25 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E592" t="n">
-        <v>222741</v>
+        <v>6425</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I592" t="inlineStr"/>
@@ -69002,13 +68983,13 @@
         </is>
       </c>
       <c r="Q592" t="n">
-        <v>487060</v>
+        <v>486944</v>
       </c>
       <c r="R592" t="n">
-        <v>7004115</v>
+        <v>7003933</v>
       </c>
       <c r="S592" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T592" t="inlineStr">
         <is>
@@ -69064,10 +69045,10 @@
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>119312764</v>
+        <v>119312537</v>
       </c>
       <c r="B593" t="n">
-        <v>97512</v>
+        <v>98502</v>
       </c>
       <c r="C593" t="inlineStr">
         <is>
@@ -69076,41 +69057,41 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>222741</v>
+        <v>220787</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I593" t="inlineStr"/>
       <c r="P593" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q593" t="n">
-        <v>486807</v>
+        <v>487060</v>
       </c>
       <c r="R593" t="n">
-        <v>7003950</v>
+        <v>7004115</v>
       </c>
       <c r="S593" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T593" t="inlineStr">
         <is>
@@ -69154,22 +69135,22 @@
       <c r="AT593" t="inlineStr"/>
       <c r="AW593" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX593" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>119310979</v>
+        <v>119312764</v>
       </c>
       <c r="B594" t="n">
-        <v>91921</v>
+        <v>97529</v>
       </c>
       <c r="C594" t="inlineStr">
         <is>
@@ -69182,37 +69163,37 @@
         </is>
       </c>
       <c r="E594" t="n">
-        <v>4769</v>
+        <v>222741</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I594" t="inlineStr"/>
       <c r="P594" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q594" t="n">
-        <v>487043</v>
+        <v>486807</v>
       </c>
       <c r="R594" t="n">
-        <v>7003935</v>
+        <v>7003950</v>
       </c>
       <c r="S594" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T594" t="inlineStr">
         <is>
@@ -69268,10 +69249,10 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>119312923</v>
+        <v>119308870</v>
       </c>
       <c r="B595" t="n">
-        <v>57640</v>
+        <v>94803</v>
       </c>
       <c r="C595" t="inlineStr">
         <is>
@@ -69280,31 +69261,31 @@
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E595" t="n">
-        <v>103021</v>
+        <v>2809</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I595" t="inlineStr"/>
       <c r="P595" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q595" t="n">
@@ -69314,7 +69295,7 @@
         <v>7004115</v>
       </c>
       <c r="S595" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T595" t="inlineStr">
         <is>
@@ -69370,10 +69351,10 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>119312982</v>
+        <v>119309504</v>
       </c>
       <c r="B596" t="n">
-        <v>91921</v>
+        <v>98502</v>
       </c>
       <c r="C596" t="inlineStr">
         <is>
@@ -69382,41 +69363,41 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E596" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I596" t="inlineStr"/>
       <c r="P596" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q596" t="n">
-        <v>486822</v>
+        <v>487056</v>
       </c>
       <c r="R596" t="n">
-        <v>7004015</v>
+        <v>7004063</v>
       </c>
       <c r="S596" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T596" t="inlineStr">
         <is>
@@ -69460,22 +69441,22 @@
       <c r="AT596" t="inlineStr"/>
       <c r="AW596" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX596" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY596" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>119308870</v>
+        <v>119311276</v>
       </c>
       <c r="B597" t="n">
-        <v>94797</v>
+        <v>90988</v>
       </c>
       <c r="C597" t="inlineStr">
         <is>
@@ -69484,41 +69465,41 @@
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E597" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I597" t="inlineStr"/>
       <c r="P597" t="inlineStr">
         <is>
-          <t>Verksmon, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q597" t="n">
-        <v>487060</v>
+        <v>487004</v>
       </c>
       <c r="R597" t="n">
-        <v>7004115</v>
+        <v>7003923</v>
       </c>
       <c r="S597" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T597" t="inlineStr">
         <is>
@@ -69562,22 +69543,22 @@
       <c r="AT597" t="inlineStr"/>
       <c r="AW597" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX597" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY597" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>119308823</v>
+        <v>119311396</v>
       </c>
       <c r="B598" t="n">
-        <v>91921</v>
+        <v>98502</v>
       </c>
       <c r="C598" t="inlineStr">
         <is>
@@ -69586,41 +69567,41 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E598" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I598" t="inlineStr"/>
       <c r="P598" t="inlineStr">
         <is>
-          <t>Verksmon, Jmt</t>
+          <t>Torvalla naturreservat, Torvalla naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q598" t="n">
-        <v>487060</v>
+        <v>486995</v>
       </c>
       <c r="R598" t="n">
-        <v>7004115</v>
+        <v>7003925</v>
       </c>
       <c r="S598" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T598" t="inlineStr">
         <is>
@@ -69664,22 +69645,22 @@
       <c r="AT598" t="inlineStr"/>
       <c r="AW598" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX598" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY598" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>119309241</v>
+        <v>119309475</v>
       </c>
       <c r="B599" t="n">
-        <v>57640</v>
+        <v>78786</v>
       </c>
       <c r="C599" t="inlineStr">
         <is>
@@ -69692,37 +69673,37 @@
         </is>
       </c>
       <c r="E599" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I599" t="inlineStr"/>
       <c r="P599" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q599" t="n">
-        <v>487066</v>
+        <v>487092</v>
       </c>
       <c r="R599" t="n">
-        <v>7004042</v>
+        <v>7004027</v>
       </c>
       <c r="S599" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T599" t="inlineStr">
         <is>
@@ -69778,10 +69759,10 @@
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>119309185</v>
+        <v>119312398</v>
       </c>
       <c r="B600" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C600" t="inlineStr">
         <is>
@@ -69818,10 +69799,10 @@
         </is>
       </c>
       <c r="Q600" t="n">
-        <v>487054</v>
+        <v>486896</v>
       </c>
       <c r="R600" t="n">
-        <v>7004058</v>
+        <v>7003946</v>
       </c>
       <c r="S600" t="n">
         <v>10</v>
@@ -69880,10 +69861,10 @@
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>119312082</v>
+        <v>119310979</v>
       </c>
       <c r="B601" t="n">
-        <v>94797</v>
+        <v>91926</v>
       </c>
       <c r="C601" t="inlineStr">
         <is>
@@ -69896,21 +69877,21 @@
         </is>
       </c>
       <c r="E601" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I601" t="inlineStr"/>
@@ -69920,13 +69901,13 @@
         </is>
       </c>
       <c r="Q601" t="n">
-        <v>486946</v>
+        <v>487043</v>
       </c>
       <c r="R601" t="n">
-        <v>7003956</v>
+        <v>7003935</v>
       </c>
       <c r="S601" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T601" t="inlineStr">
         <is>
@@ -69970,12 +69951,12 @@
       <c r="AT601" t="inlineStr"/>
       <c r="AW601" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX601" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY601" t="inlineStr"/>
@@ -69985,7 +69966,7 @@
         <v>119311193</v>
       </c>
       <c r="B602" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C602" t="inlineStr">
         <is>
@@ -70084,10 +70065,10 @@
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>119312223</v>
+        <v>119312923</v>
       </c>
       <c r="B603" t="n">
-        <v>97512</v>
+        <v>57643</v>
       </c>
       <c r="C603" t="inlineStr">
         <is>
@@ -70096,25 +70077,25 @@
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E603" t="n">
-        <v>222741</v>
+        <v>103021</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I603" t="inlineStr"/>
@@ -70124,10 +70105,10 @@
         </is>
       </c>
       <c r="Q603" t="n">
-        <v>486946</v>
+        <v>487060</v>
       </c>
       <c r="R603" t="n">
-        <v>7003956</v>
+        <v>7004115</v>
       </c>
       <c r="S603" t="n">
         <v>10</v>
@@ -70186,10 +70167,10 @@
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>119311396</v>
+        <v>119312547</v>
       </c>
       <c r="B604" t="n">
-        <v>98396</v>
+        <v>97529</v>
       </c>
       <c r="C604" t="inlineStr">
         <is>
@@ -70198,41 +70179,41 @@
       </c>
       <c r="D604" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E604" t="n">
-        <v>220787</v>
+        <v>222741</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I604" t="inlineStr"/>
       <c r="P604" t="inlineStr">
         <is>
-          <t>Torvalla naturreservat, Torvalla naturreservat, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q604" t="n">
-        <v>486995</v>
+        <v>487060</v>
       </c>
       <c r="R604" t="n">
-        <v>7003925</v>
+        <v>7004115</v>
       </c>
       <c r="S604" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T604" t="inlineStr">
         <is>
@@ -70276,12 +70257,12 @@
       <c r="AT604" t="inlineStr"/>
       <c r="AW604" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX604" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY604" t="inlineStr"/>

--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -65104,10 +65104,10 @@
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>119312412</v>
+        <v>119310718</v>
       </c>
       <c r="B560" t="n">
-        <v>97428</v>
+        <v>78788</v>
       </c>
       <c r="C560" t="inlineStr">
         <is>
@@ -65116,41 +65116,41 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E560" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I560" t="inlineStr"/>
       <c r="P560" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q560" t="n">
-        <v>486896</v>
+        <v>487060</v>
       </c>
       <c r="R560" t="n">
-        <v>7003946</v>
+        <v>7004115</v>
       </c>
       <c r="S560" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T560" t="inlineStr">
         <is>
@@ -65194,22 +65194,22 @@
       <c r="AT560" t="inlineStr"/>
       <c r="AW560" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX560" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>119310718</v>
+        <v>119312412</v>
       </c>
       <c r="B561" t="n">
-        <v>78788</v>
+        <v>97428</v>
       </c>
       <c r="C561" t="inlineStr">
         <is>
@@ -65218,41 +65218,41 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E561" t="n">
-        <v>6425</v>
+        <v>221063</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I561" t="inlineStr"/>
       <c r="P561" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q561" t="n">
-        <v>487060</v>
+        <v>486896</v>
       </c>
       <c r="R561" t="n">
-        <v>7004115</v>
+        <v>7003946</v>
       </c>
       <c r="S561" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T561" t="inlineStr">
         <is>
@@ -65296,12 +65296,12 @@
       <c r="AT561" t="inlineStr"/>
       <c r="AW561" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX561" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY561" t="inlineStr"/>

--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -65104,10 +65104,10 @@
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>119310718</v>
+        <v>119312412</v>
       </c>
       <c r="B560" t="n">
-        <v>78788</v>
+        <v>97428</v>
       </c>
       <c r="C560" t="inlineStr">
         <is>
@@ -65116,41 +65116,41 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E560" t="n">
-        <v>6425</v>
+        <v>221063</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I560" t="inlineStr"/>
       <c r="P560" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q560" t="n">
-        <v>487060</v>
+        <v>486896</v>
       </c>
       <c r="R560" t="n">
-        <v>7004115</v>
+        <v>7003946</v>
       </c>
       <c r="S560" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T560" t="inlineStr">
         <is>
@@ -65194,22 +65194,22 @@
       <c r="AT560" t="inlineStr"/>
       <c r="AW560" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX560" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>119312412</v>
+        <v>119310718</v>
       </c>
       <c r="B561" t="n">
-        <v>97428</v>
+        <v>78788</v>
       </c>
       <c r="C561" t="inlineStr">
         <is>
@@ -65218,41 +65218,41 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E561" t="n">
-        <v>221063</v>
+        <v>6425</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I561" t="inlineStr"/>
       <c r="P561" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q561" t="n">
-        <v>486896</v>
+        <v>487060</v>
       </c>
       <c r="R561" t="n">
-        <v>7003946</v>
+        <v>7004115</v>
       </c>
       <c r="S561" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T561" t="inlineStr">
         <is>
@@ -65296,12 +65296,12 @@
       <c r="AT561" t="inlineStr"/>
       <c r="AW561" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX561" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY561" t="inlineStr"/>

--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -62836,10 +62836,10 @@
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>119312082</v>
+        <v>119310979</v>
       </c>
       <c r="B538" t="n">
-        <v>94805</v>
+        <v>91928</v>
       </c>
       <c r="C538" t="inlineStr">
         <is>
@@ -62852,21 +62852,21 @@
         </is>
       </c>
       <c r="E538" t="n">
-        <v>2809</v>
+        <v>4769</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I538" t="inlineStr"/>
@@ -62876,13 +62876,13 @@
         </is>
       </c>
       <c r="Q538" t="n">
-        <v>486946</v>
+        <v>487043</v>
       </c>
       <c r="R538" t="n">
-        <v>7003956</v>
+        <v>7003935</v>
       </c>
       <c r="S538" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T538" t="inlineStr">
         <is>
@@ -62926,22 +62926,22 @@
       <c r="AT538" t="inlineStr"/>
       <c r="AW538" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX538" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>119311723</v>
+        <v>119311396</v>
       </c>
       <c r="B539" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C539" t="inlineStr">
         <is>
@@ -62972,24 +62972,19 @@
         </is>
       </c>
       <c r="I539" t="inlineStr"/>
-      <c r="K539" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P539" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Torvalla naturreservat, Torvalla naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q539" t="n">
-        <v>486946</v>
+        <v>486995</v>
       </c>
       <c r="R539" t="n">
-        <v>7003956</v>
+        <v>7003925</v>
       </c>
       <c r="S539" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T539" t="inlineStr">
         <is>
@@ -63033,22 +63028,22 @@
       <c r="AT539" t="inlineStr"/>
       <c r="AW539" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX539" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>119309495</v>
+        <v>119311857</v>
       </c>
       <c r="B540" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C540" t="inlineStr">
         <is>
@@ -63057,46 +63052,41 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E540" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I540" t="inlineStr"/>
-      <c r="J540" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P540" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q540" t="n">
-        <v>487056</v>
+        <v>486943</v>
       </c>
       <c r="R540" t="n">
-        <v>7004063</v>
+        <v>7003953</v>
       </c>
       <c r="S540" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T540" t="inlineStr">
         <is>
@@ -63140,22 +63130,22 @@
       <c r="AT540" t="inlineStr"/>
       <c r="AW540" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX540" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>119308623</v>
+        <v>119311723</v>
       </c>
       <c r="B541" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C541" t="inlineStr">
         <is>
@@ -63185,16 +63175,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I541" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J541" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I541" t="inlineStr"/>
       <c r="K541" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -63206,13 +63187,13 @@
         </is>
       </c>
       <c r="Q541" t="n">
-        <v>487060</v>
+        <v>486946</v>
       </c>
       <c r="R541" t="n">
-        <v>7004115</v>
+        <v>7003956</v>
       </c>
       <c r="S541" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T541" t="inlineStr">
         <is>
@@ -63268,10 +63249,10 @@
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>119312764</v>
+        <v>119309475</v>
       </c>
       <c r="B542" t="n">
-        <v>97531</v>
+        <v>78788</v>
       </c>
       <c r="C542" t="inlineStr">
         <is>
@@ -63280,38 +63261,38 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E542" t="n">
-        <v>222741</v>
+        <v>6425</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I542" t="inlineStr"/>
       <c r="P542" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q542" t="n">
-        <v>486807</v>
+        <v>487092</v>
       </c>
       <c r="R542" t="n">
-        <v>7003950</v>
+        <v>7004027</v>
       </c>
       <c r="S542" t="n">
         <v>10</v>
@@ -63370,10 +63351,10 @@
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>119312398</v>
+        <v>119309241</v>
       </c>
       <c r="B543" t="n">
-        <v>98504</v>
+        <v>57644</v>
       </c>
       <c r="C543" t="inlineStr">
         <is>
@@ -63382,25 +63363,25 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E543" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I543" t="inlineStr"/>
@@ -63410,13 +63391,13 @@
         </is>
       </c>
       <c r="Q543" t="n">
-        <v>486896</v>
+        <v>487066</v>
       </c>
       <c r="R543" t="n">
-        <v>7003946</v>
+        <v>7004042</v>
       </c>
       <c r="S543" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T543" t="inlineStr">
         <is>
@@ -63472,10 +63453,10 @@
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>119312547</v>
+        <v>119308689</v>
       </c>
       <c r="B544" t="n">
-        <v>97531</v>
+        <v>98079</v>
       </c>
       <c r="C544" t="inlineStr">
         <is>
@@ -63484,28 +63465,42 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E544" t="n">
-        <v>222741</v>
+        <v>220787</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I544" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P544" t="inlineStr">
         <is>
           <t>Verksmon, Verksmon, Jmt</t>
@@ -63574,10 +63569,10 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>119312923</v>
+        <v>119312223</v>
       </c>
       <c r="B545" t="n">
-        <v>57644</v>
+        <v>97106</v>
       </c>
       <c r="C545" t="inlineStr">
         <is>
@@ -63586,25 +63581,25 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E545" t="n">
-        <v>103021</v>
+        <v>222741</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I545" t="inlineStr"/>
@@ -63614,10 +63609,10 @@
         </is>
       </c>
       <c r="Q545" t="n">
-        <v>487060</v>
+        <v>486946</v>
       </c>
       <c r="R545" t="n">
-        <v>7004115</v>
+        <v>7003956</v>
       </c>
       <c r="S545" t="n">
         <v>10</v>
@@ -63676,10 +63671,10 @@
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>119312434</v>
+        <v>119312082</v>
       </c>
       <c r="B546" t="n">
-        <v>105505</v>
+        <v>95313</v>
       </c>
       <c r="C546" t="inlineStr">
         <is>
@@ -63692,34 +63687,34 @@
         </is>
       </c>
       <c r="E546" t="n">
-        <v>221725</v>
+        <v>2809</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I546" t="inlineStr"/>
       <c r="P546" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q546" t="n">
-        <v>486896</v>
+        <v>486946</v>
       </c>
       <c r="R546" t="n">
-        <v>7003946</v>
+        <v>7003956</v>
       </c>
       <c r="S546" t="n">
         <v>10</v>
@@ -63766,22 +63761,22 @@
       <c r="AT546" t="inlineStr"/>
       <c r="AW546" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX546" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>119308870</v>
+        <v>119313051</v>
       </c>
       <c r="B547" t="n">
-        <v>94805</v>
+        <v>78788</v>
       </c>
       <c r="C547" t="inlineStr">
         <is>
@@ -63790,41 +63785,41 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E547" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I547" t="inlineStr"/>
       <c r="P547" t="inlineStr">
         <is>
-          <t>Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q547" t="n">
-        <v>487060</v>
+        <v>486843</v>
       </c>
       <c r="R547" t="n">
-        <v>7004115</v>
+        <v>7004053</v>
       </c>
       <c r="S547" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T547" t="inlineStr">
         <is>
@@ -63868,22 +63863,22 @@
       <c r="AT547" t="inlineStr"/>
       <c r="AW547" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX547" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>119312982</v>
+        <v>119309504</v>
       </c>
       <c r="B548" t="n">
-        <v>91928</v>
+        <v>98079</v>
       </c>
       <c r="C548" t="inlineStr">
         <is>
@@ -63892,41 +63887,41 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E548" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I548" t="inlineStr"/>
       <c r="P548" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q548" t="n">
-        <v>486822</v>
+        <v>487056</v>
       </c>
       <c r="R548" t="n">
-        <v>7004015</v>
+        <v>7004063</v>
       </c>
       <c r="S548" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T548" t="inlineStr">
         <is>
@@ -63970,22 +63965,22 @@
       <c r="AT548" t="inlineStr"/>
       <c r="AW548" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX548" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>119311630</v>
+        <v>119308823</v>
       </c>
       <c r="B549" t="n">
-        <v>78788</v>
+        <v>91928</v>
       </c>
       <c r="C549" t="inlineStr">
         <is>
@@ -63994,41 +63989,41 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E549" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I549" t="inlineStr"/>
       <c r="P549" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q549" t="n">
-        <v>486944</v>
+        <v>487060</v>
       </c>
       <c r="R549" t="n">
-        <v>7003933</v>
+        <v>7004115</v>
       </c>
       <c r="S549" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T549" t="inlineStr">
         <is>
@@ -64084,10 +64079,10 @@
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>119313079</v>
+        <v>119312982</v>
       </c>
       <c r="B550" t="n">
-        <v>78788</v>
+        <v>91928</v>
       </c>
       <c r="C550" t="inlineStr">
         <is>
@@ -64096,25 +64091,25 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E550" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I550" t="inlineStr"/>
@@ -64124,13 +64119,13 @@
         </is>
       </c>
       <c r="Q550" t="n">
-        <v>486834</v>
+        <v>486822</v>
       </c>
       <c r="R550" t="n">
-        <v>7004097</v>
+        <v>7004015</v>
       </c>
       <c r="S550" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T550" t="inlineStr">
         <is>
@@ -64186,10 +64181,10 @@
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>119312223</v>
+        <v>119312398</v>
       </c>
       <c r="B551" t="n">
-        <v>97531</v>
+        <v>98079</v>
       </c>
       <c r="C551" t="inlineStr">
         <is>
@@ -64198,38 +64193,38 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E551" t="n">
-        <v>222741</v>
+        <v>220787</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I551" t="inlineStr"/>
       <c r="P551" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q551" t="n">
-        <v>486946</v>
+        <v>486896</v>
       </c>
       <c r="R551" t="n">
-        <v>7003956</v>
+        <v>7003946</v>
       </c>
       <c r="S551" t="n">
         <v>10</v>
@@ -64276,22 +64271,22 @@
       <c r="AT551" t="inlineStr"/>
       <c r="AW551" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX551" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>119309475</v>
+        <v>119311276</v>
       </c>
       <c r="B552" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C552" t="inlineStr">
         <is>
@@ -64304,21 +64299,21 @@
         </is>
       </c>
       <c r="E552" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I552" t="inlineStr"/>
@@ -64328,13 +64323,13 @@
         </is>
       </c>
       <c r="Q552" t="n">
-        <v>487092</v>
+        <v>487004</v>
       </c>
       <c r="R552" t="n">
-        <v>7004027</v>
+        <v>7003923</v>
       </c>
       <c r="S552" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T552" t="inlineStr">
         <is>
@@ -64390,10 +64385,10 @@
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>119311857</v>
+        <v>119312547</v>
       </c>
       <c r="B553" t="n">
-        <v>90990</v>
+        <v>97106</v>
       </c>
       <c r="C553" t="inlineStr">
         <is>
@@ -64402,41 +64397,41 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E553" t="n">
-        <v>1202</v>
+        <v>222741</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I553" t="inlineStr"/>
       <c r="P553" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q553" t="n">
-        <v>486943</v>
+        <v>487060</v>
       </c>
       <c r="R553" t="n">
-        <v>7003953</v>
+        <v>7004115</v>
       </c>
       <c r="S553" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T553" t="inlineStr">
         <is>
@@ -64480,22 +64475,22 @@
       <c r="AT553" t="inlineStr"/>
       <c r="AW553" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX553" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>119310979</v>
+        <v>119313079</v>
       </c>
       <c r="B554" t="n">
-        <v>91928</v>
+        <v>78788</v>
       </c>
       <c r="C554" t="inlineStr">
         <is>
@@ -64504,41 +64499,41 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E554" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I554" t="inlineStr"/>
       <c r="P554" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q554" t="n">
-        <v>487043</v>
+        <v>486834</v>
       </c>
       <c r="R554" t="n">
-        <v>7003935</v>
+        <v>7004097</v>
       </c>
       <c r="S554" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T554" t="inlineStr">
         <is>
@@ -64594,10 +64589,10 @@
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>119309185</v>
+        <v>119311193</v>
       </c>
       <c r="B555" t="n">
-        <v>98504</v>
+        <v>78788</v>
       </c>
       <c r="C555" t="inlineStr">
         <is>
@@ -64606,41 +64601,41 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E555" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I555" t="inlineStr"/>
       <c r="P555" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q555" t="n">
-        <v>487054</v>
+        <v>487004</v>
       </c>
       <c r="R555" t="n">
-        <v>7004058</v>
+        <v>7003923</v>
       </c>
       <c r="S555" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T555" t="inlineStr">
         <is>
@@ -64696,7 +64691,7 @@
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>119309241</v>
+        <v>119312923</v>
       </c>
       <c r="B556" t="n">
         <v>57644</v>
@@ -64732,17 +64727,17 @@
       <c r="I556" t="inlineStr"/>
       <c r="P556" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q556" t="n">
-        <v>487066</v>
+        <v>487060</v>
       </c>
       <c r="R556" t="n">
-        <v>7004042</v>
+        <v>7004115</v>
       </c>
       <c r="S556" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T556" t="inlineStr">
         <is>
@@ -64786,22 +64781,22 @@
       <c r="AT556" t="inlineStr"/>
       <c r="AW556" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX556" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>119311193</v>
+        <v>119309185</v>
       </c>
       <c r="B557" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C557" t="inlineStr">
         <is>
@@ -64810,41 +64805,41 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E557" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I557" t="inlineStr"/>
       <c r="P557" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q557" t="n">
-        <v>487004</v>
+        <v>487054</v>
       </c>
       <c r="R557" t="n">
-        <v>7003923</v>
+        <v>7004058</v>
       </c>
       <c r="S557" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T557" t="inlineStr">
         <is>
@@ -64900,10 +64895,10 @@
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>119311276</v>
+        <v>119308870</v>
       </c>
       <c r="B558" t="n">
-        <v>90990</v>
+        <v>95313</v>
       </c>
       <c r="C558" t="inlineStr">
         <is>
@@ -64912,41 +64907,41 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E558" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I558" t="inlineStr"/>
       <c r="P558" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q558" t="n">
-        <v>487004</v>
+        <v>487060</v>
       </c>
       <c r="R558" t="n">
-        <v>7003923</v>
+        <v>7004115</v>
       </c>
       <c r="S558" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T558" t="inlineStr">
         <is>
@@ -64990,22 +64985,22 @@
       <c r="AT558" t="inlineStr"/>
       <c r="AW558" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX558" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY558" t="inlineStr"/>
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>119313051</v>
+        <v>119312434</v>
       </c>
       <c r="B559" t="n">
-        <v>78788</v>
+        <v>105080</v>
       </c>
       <c r="C559" t="inlineStr">
         <is>
@@ -65014,25 +65009,25 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E559" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I559" t="inlineStr"/>
@@ -65042,10 +65037,10 @@
         </is>
       </c>
       <c r="Q559" t="n">
-        <v>486843</v>
+        <v>486896</v>
       </c>
       <c r="R559" t="n">
-        <v>7004053</v>
+        <v>7003946</v>
       </c>
       <c r="S559" t="n">
         <v>10</v>
@@ -65104,10 +65099,10 @@
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>119312412</v>
+        <v>119312764</v>
       </c>
       <c r="B560" t="n">
-        <v>97428</v>
+        <v>97106</v>
       </c>
       <c r="C560" t="inlineStr">
         <is>
@@ -65120,21 +65115,21 @@
         </is>
       </c>
       <c r="E560" t="n">
-        <v>221063</v>
+        <v>222741</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I560" t="inlineStr"/>
@@ -65144,10 +65139,10 @@
         </is>
       </c>
       <c r="Q560" t="n">
-        <v>486896</v>
+        <v>486807</v>
       </c>
       <c r="R560" t="n">
-        <v>7003946</v>
+        <v>7003950</v>
       </c>
       <c r="S560" t="n">
         <v>10</v>
@@ -65308,10 +65303,10 @@
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>119311396</v>
+        <v>119311630</v>
       </c>
       <c r="B562" t="n">
-        <v>98504</v>
+        <v>78788</v>
       </c>
       <c r="C562" t="inlineStr">
         <is>
@@ -65320,41 +65315,41 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E562" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I562" t="inlineStr"/>
       <c r="P562" t="inlineStr">
         <is>
-          <t>Torvalla naturreservat, Torvalla naturreservat, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q562" t="n">
-        <v>486995</v>
+        <v>486944</v>
       </c>
       <c r="R562" t="n">
-        <v>7003925</v>
+        <v>7003933</v>
       </c>
       <c r="S562" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T562" t="inlineStr">
         <is>
@@ -65398,22 +65393,22 @@
       <c r="AT562" t="inlineStr"/>
       <c r="AW562" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX562" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>119308823</v>
+        <v>119312412</v>
       </c>
       <c r="B563" t="n">
-        <v>91928</v>
+        <v>97003</v>
       </c>
       <c r="C563" t="inlineStr">
         <is>
@@ -65426,37 +65421,37 @@
         </is>
       </c>
       <c r="E563" t="n">
-        <v>4769</v>
+        <v>221063</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I563" t="inlineStr"/>
       <c r="P563" t="inlineStr">
         <is>
-          <t>Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q563" t="n">
-        <v>487060</v>
+        <v>486896</v>
       </c>
       <c r="R563" t="n">
-        <v>7004115</v>
+        <v>7003946</v>
       </c>
       <c r="S563" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T563" t="inlineStr">
         <is>
@@ -65500,12 +65495,12 @@
       <c r="AT563" t="inlineStr"/>
       <c r="AW563" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX563" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY563" t="inlineStr"/>

--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -63040,10 +63040,10 @@
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>119311857</v>
+        <v>119309475</v>
       </c>
       <c r="B540" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C540" t="inlineStr">
         <is>
@@ -63056,37 +63056,37 @@
         </is>
       </c>
       <c r="E540" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I540" t="inlineStr"/>
       <c r="P540" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q540" t="n">
-        <v>486943</v>
+        <v>487092</v>
       </c>
       <c r="R540" t="n">
-        <v>7003953</v>
+        <v>7004027</v>
       </c>
       <c r="S540" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T540" t="inlineStr">
         <is>
@@ -63142,10 +63142,10 @@
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>119311723</v>
+        <v>119311857</v>
       </c>
       <c r="B541" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C541" t="inlineStr">
         <is>
@@ -63154,46 +63154,41 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E541" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I541" t="inlineStr"/>
-      <c r="K541" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P541" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q541" t="n">
-        <v>486946</v>
+        <v>486943</v>
       </c>
       <c r="R541" t="n">
-        <v>7003956</v>
+        <v>7003953</v>
       </c>
       <c r="S541" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T541" t="inlineStr">
         <is>
@@ -63237,22 +63232,22 @@
       <c r="AT541" t="inlineStr"/>
       <c r="AW541" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX541" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>119309475</v>
+        <v>119311723</v>
       </c>
       <c r="B542" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C542" t="inlineStr">
         <is>
@@ -63261,41 +63256,46 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E542" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P542" t="inlineStr">
         <is>
           <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q542" t="n">
-        <v>487092</v>
+        <v>486946</v>
       </c>
       <c r="R542" t="n">
-        <v>7004027</v>
+        <v>7003956</v>
       </c>
       <c r="S542" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T542" t="inlineStr">
         <is>
@@ -63339,12 +63339,12 @@
       <c r="AT542" t="inlineStr"/>
       <c r="AW542" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX542" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY542" t="inlineStr"/>

--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -62836,10 +62836,10 @@
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>119310979</v>
+        <v>119311193</v>
       </c>
       <c r="B538" t="n">
-        <v>91928</v>
+        <v>78788</v>
       </c>
       <c r="C538" t="inlineStr">
         <is>
@@ -62848,25 +62848,25 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E538" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I538" t="inlineStr"/>
@@ -62876,10 +62876,10 @@
         </is>
       </c>
       <c r="Q538" t="n">
-        <v>487043</v>
+        <v>487004</v>
       </c>
       <c r="R538" t="n">
-        <v>7003935</v>
+        <v>7003923</v>
       </c>
       <c r="S538" t="n">
         <v>20</v>
@@ -62938,10 +62938,10 @@
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>119311396</v>
+        <v>119312082</v>
       </c>
       <c r="B539" t="n">
-        <v>98079</v>
+        <v>95313</v>
       </c>
       <c r="C539" t="inlineStr">
         <is>
@@ -62950,41 +62950,41 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E539" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I539" t="inlineStr"/>
       <c r="P539" t="inlineStr">
         <is>
-          <t>Torvalla naturreservat, Torvalla naturreservat, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q539" t="n">
-        <v>486995</v>
+        <v>486946</v>
       </c>
       <c r="R539" t="n">
-        <v>7003925</v>
+        <v>7003956</v>
       </c>
       <c r="S539" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T539" t="inlineStr">
         <is>
@@ -63028,22 +63028,22 @@
       <c r="AT539" t="inlineStr"/>
       <c r="AW539" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX539" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>119309475</v>
+        <v>119312537</v>
       </c>
       <c r="B540" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C540" t="inlineStr">
         <is>
@@ -63052,25 +63052,25 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E540" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I540" t="inlineStr"/>
@@ -63080,13 +63080,13 @@
         </is>
       </c>
       <c r="Q540" t="n">
-        <v>487092</v>
+        <v>487060</v>
       </c>
       <c r="R540" t="n">
-        <v>7004027</v>
+        <v>7004115</v>
       </c>
       <c r="S540" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T540" t="inlineStr">
         <is>
@@ -63130,22 +63130,22 @@
       <c r="AT540" t="inlineStr"/>
       <c r="AW540" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX540" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>119311857</v>
+        <v>119311723</v>
       </c>
       <c r="B541" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C541" t="inlineStr">
         <is>
@@ -63154,41 +63154,46 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E541" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P541" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q541" t="n">
-        <v>486943</v>
+        <v>486946</v>
       </c>
       <c r="R541" t="n">
-        <v>7003953</v>
+        <v>7003956</v>
       </c>
       <c r="S541" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T541" t="inlineStr">
         <is>
@@ -63232,22 +63237,22 @@
       <c r="AT541" t="inlineStr"/>
       <c r="AW541" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX541" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>119311723</v>
+        <v>119312547</v>
       </c>
       <c r="B542" t="n">
-        <v>98079</v>
+        <v>97106</v>
       </c>
       <c r="C542" t="inlineStr">
         <is>
@@ -63256,46 +63261,41 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E542" t="n">
-        <v>220787</v>
+        <v>222741</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I542" t="inlineStr"/>
-      <c r="K542" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P542" t="inlineStr">
         <is>
           <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q542" t="n">
-        <v>486946</v>
+        <v>487060</v>
       </c>
       <c r="R542" t="n">
-        <v>7003956</v>
+        <v>7004115</v>
       </c>
       <c r="S542" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T542" t="inlineStr">
         <is>
@@ -63351,10 +63351,10 @@
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>119309241</v>
+        <v>119312764</v>
       </c>
       <c r="B543" t="n">
-        <v>57644</v>
+        <v>97106</v>
       </c>
       <c r="C543" t="inlineStr">
         <is>
@@ -63363,25 +63363,25 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E543" t="n">
-        <v>103021</v>
+        <v>222741</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I543" t="inlineStr"/>
@@ -63391,13 +63391,13 @@
         </is>
       </c>
       <c r="Q543" t="n">
-        <v>487066</v>
+        <v>486807</v>
       </c>
       <c r="R543" t="n">
-        <v>7004042</v>
+        <v>7003950</v>
       </c>
       <c r="S543" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T543" t="inlineStr">
         <is>
@@ -63453,10 +63453,10 @@
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>119308689</v>
+        <v>119311630</v>
       </c>
       <c r="B544" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C544" t="inlineStr">
         <is>
@@ -63465,55 +63465,41 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E544" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I544" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J544" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K544" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr"/>
       <c r="P544" t="inlineStr">
         <is>
           <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q544" t="n">
-        <v>487060</v>
+        <v>486944</v>
       </c>
       <c r="R544" t="n">
-        <v>7004115</v>
+        <v>7003933</v>
       </c>
       <c r="S544" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T544" t="inlineStr">
         <is>
@@ -63671,10 +63657,10 @@
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>119312082</v>
+        <v>119311396</v>
       </c>
       <c r="B546" t="n">
-        <v>95313</v>
+        <v>98079</v>
       </c>
       <c r="C546" t="inlineStr">
         <is>
@@ -63683,41 +63669,41 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E546" t="n">
-        <v>2809</v>
+        <v>220787</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I546" t="inlineStr"/>
       <c r="P546" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Torvalla naturreservat, Torvalla naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q546" t="n">
-        <v>486946</v>
+        <v>486995</v>
       </c>
       <c r="R546" t="n">
-        <v>7003956</v>
+        <v>7003925</v>
       </c>
       <c r="S546" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T546" t="inlineStr">
         <is>
@@ -63761,22 +63747,22 @@
       <c r="AT546" t="inlineStr"/>
       <c r="AW546" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX546" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY546" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>119313051</v>
+        <v>119312412</v>
       </c>
       <c r="B547" t="n">
-        <v>78788</v>
+        <v>97003</v>
       </c>
       <c r="C547" t="inlineStr">
         <is>
@@ -63785,25 +63771,25 @@
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E547" t="n">
-        <v>6425</v>
+        <v>221063</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I547" t="inlineStr"/>
@@ -63813,10 +63799,10 @@
         </is>
       </c>
       <c r="Q547" t="n">
-        <v>486843</v>
+        <v>486896</v>
       </c>
       <c r="R547" t="n">
-        <v>7004053</v>
+        <v>7003946</v>
       </c>
       <c r="S547" t="n">
         <v>10</v>
@@ -63875,10 +63861,10 @@
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>119309504</v>
+        <v>119313051</v>
       </c>
       <c r="B548" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C548" t="inlineStr">
         <is>
@@ -63887,41 +63873,41 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E548" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I548" t="inlineStr"/>
       <c r="P548" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q548" t="n">
-        <v>487056</v>
+        <v>486843</v>
       </c>
       <c r="R548" t="n">
-        <v>7004063</v>
+        <v>7004053</v>
       </c>
       <c r="S548" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T548" t="inlineStr">
         <is>
@@ -63965,19 +63951,19 @@
       <c r="AT548" t="inlineStr"/>
       <c r="AW548" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX548" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>119308823</v>
+        <v>119310979</v>
       </c>
       <c r="B549" t="n">
         <v>91928</v>
@@ -64013,17 +63999,17 @@
       <c r="I549" t="inlineStr"/>
       <c r="P549" t="inlineStr">
         <is>
-          <t>Verksmon, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q549" t="n">
-        <v>487060</v>
+        <v>487043</v>
       </c>
       <c r="R549" t="n">
-        <v>7004115</v>
+        <v>7003935</v>
       </c>
       <c r="S549" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T549" t="inlineStr">
         <is>
@@ -64067,22 +64053,22 @@
       <c r="AT549" t="inlineStr"/>
       <c r="AW549" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX549" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY549" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>119312982</v>
+        <v>119309504</v>
       </c>
       <c r="B550" t="n">
-        <v>91928</v>
+        <v>98079</v>
       </c>
       <c r="C550" t="inlineStr">
         <is>
@@ -64091,41 +64077,41 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E550" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I550" t="inlineStr"/>
       <c r="P550" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q550" t="n">
-        <v>486822</v>
+        <v>487056</v>
       </c>
       <c r="R550" t="n">
-        <v>7004015</v>
+        <v>7004063</v>
       </c>
       <c r="S550" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="T550" t="inlineStr">
         <is>
@@ -64169,22 +64155,22 @@
       <c r="AT550" t="inlineStr"/>
       <c r="AW550" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX550" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY550" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>119312398</v>
+        <v>119313079</v>
       </c>
       <c r="B551" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C551" t="inlineStr">
         <is>
@@ -64193,25 +64179,25 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E551" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I551" t="inlineStr"/>
@@ -64221,10 +64207,10 @@
         </is>
       </c>
       <c r="Q551" t="n">
-        <v>486896</v>
+        <v>486834</v>
       </c>
       <c r="R551" t="n">
-        <v>7003946</v>
+        <v>7004097</v>
       </c>
       <c r="S551" t="n">
         <v>10</v>
@@ -64283,7 +64269,7 @@
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>119311276</v>
+        <v>119311857</v>
       </c>
       <c r="B552" t="n">
         <v>90990</v>
@@ -64319,14 +64305,14 @@
       <c r="I552" t="inlineStr"/>
       <c r="P552" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q552" t="n">
-        <v>487004</v>
+        <v>486943</v>
       </c>
       <c r="R552" t="n">
-        <v>7003923</v>
+        <v>7003953</v>
       </c>
       <c r="S552" t="n">
         <v>20</v>
@@ -64385,10 +64371,10 @@
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>119312547</v>
+        <v>119312531</v>
       </c>
       <c r="B553" t="n">
-        <v>97106</v>
+        <v>105080</v>
       </c>
       <c r="C553" t="inlineStr">
         <is>
@@ -64401,37 +64387,37 @@
         </is>
       </c>
       <c r="E553" t="n">
-        <v>222741</v>
+        <v>221725</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I553" t="inlineStr"/>
       <c r="P553" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q553" t="n">
-        <v>487060</v>
+        <v>486896</v>
       </c>
       <c r="R553" t="n">
-        <v>7004115</v>
+        <v>7003946</v>
       </c>
       <c r="S553" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T553" t="inlineStr">
         <is>
@@ -64475,22 +64461,22 @@
       <c r="AT553" t="inlineStr"/>
       <c r="AW553" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX553" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>119313079</v>
+        <v>119308870</v>
       </c>
       <c r="B554" t="n">
-        <v>78788</v>
+        <v>95313</v>
       </c>
       <c r="C554" t="inlineStr">
         <is>
@@ -64499,41 +64485,41 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E554" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I554" t="inlineStr"/>
       <c r="P554" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q554" t="n">
-        <v>486834</v>
+        <v>487060</v>
       </c>
       <c r="R554" t="n">
-        <v>7004097</v>
+        <v>7004115</v>
       </c>
       <c r="S554" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T554" t="inlineStr">
         <is>
@@ -64577,22 +64563,22 @@
       <c r="AT554" t="inlineStr"/>
       <c r="AW554" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX554" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>119311193</v>
+        <v>119312982</v>
       </c>
       <c r="B555" t="n">
-        <v>78788</v>
+        <v>91928</v>
       </c>
       <c r="C555" t="inlineStr">
         <is>
@@ -64601,38 +64587,38 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E555" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I555" t="inlineStr"/>
       <c r="P555" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q555" t="n">
-        <v>487004</v>
+        <v>486822</v>
       </c>
       <c r="R555" t="n">
-        <v>7003923</v>
+        <v>7004015</v>
       </c>
       <c r="S555" t="n">
         <v>20</v>
@@ -64691,10 +64677,10 @@
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>119312923</v>
+        <v>119311276</v>
       </c>
       <c r="B556" t="n">
-        <v>57644</v>
+        <v>90990</v>
       </c>
       <c r="C556" t="inlineStr">
         <is>
@@ -64707,21 +64693,21 @@
         </is>
       </c>
       <c r="E556" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I556" t="inlineStr"/>
@@ -64731,13 +64717,13 @@
         </is>
       </c>
       <c r="Q556" t="n">
-        <v>487060</v>
+        <v>487004</v>
       </c>
       <c r="R556" t="n">
-        <v>7004115</v>
+        <v>7003923</v>
       </c>
       <c r="S556" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T556" t="inlineStr">
         <is>
@@ -64781,12 +64767,12 @@
       <c r="AT556" t="inlineStr"/>
       <c r="AW556" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX556" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY556" t="inlineStr"/>
@@ -64895,10 +64881,10 @@
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>119308870</v>
+        <v>119312923</v>
       </c>
       <c r="B558" t="n">
-        <v>95313</v>
+        <v>57644</v>
       </c>
       <c r="C558" t="inlineStr">
         <is>
@@ -64907,31 +64893,31 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E558" t="n">
-        <v>2809</v>
+        <v>103021</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I558" t="inlineStr"/>
       <c r="P558" t="inlineStr">
         <is>
-          <t>Verksmon, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q558" t="n">
@@ -64941,7 +64927,7 @@
         <v>7004115</v>
       </c>
       <c r="S558" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T558" t="inlineStr">
         <is>
@@ -64997,10 +64983,10 @@
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>119312434</v>
+        <v>119310718</v>
       </c>
       <c r="B559" t="n">
-        <v>105080</v>
+        <v>78788</v>
       </c>
       <c r="C559" t="inlineStr">
         <is>
@@ -65009,41 +64995,41 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E559" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I559" t="inlineStr"/>
       <c r="P559" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q559" t="n">
-        <v>486896</v>
+        <v>487060</v>
       </c>
       <c r="R559" t="n">
-        <v>7003946</v>
+        <v>7004115</v>
       </c>
       <c r="S559" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T559" t="inlineStr">
         <is>
@@ -65087,22 +65073,22 @@
       <c r="AT559" t="inlineStr"/>
       <c r="AW559" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX559" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>119312764</v>
+        <v>119308823</v>
       </c>
       <c r="B560" t="n">
-        <v>97106</v>
+        <v>91928</v>
       </c>
       <c r="C560" t="inlineStr">
         <is>
@@ -65115,37 +65101,37 @@
         </is>
       </c>
       <c r="E560" t="n">
-        <v>222741</v>
+        <v>4769</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I560" t="inlineStr"/>
       <c r="P560" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q560" t="n">
-        <v>486807</v>
+        <v>487060</v>
       </c>
       <c r="R560" t="n">
-        <v>7003950</v>
+        <v>7004115</v>
       </c>
       <c r="S560" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T560" t="inlineStr">
         <is>
@@ -65189,22 +65175,22 @@
       <c r="AT560" t="inlineStr"/>
       <c r="AW560" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX560" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>119310718</v>
+        <v>119312398</v>
       </c>
       <c r="B561" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C561" t="inlineStr">
         <is>
@@ -65213,41 +65199,41 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E561" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I561" t="inlineStr"/>
       <c r="P561" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q561" t="n">
-        <v>487060</v>
+        <v>486896</v>
       </c>
       <c r="R561" t="n">
-        <v>7004115</v>
+        <v>7003946</v>
       </c>
       <c r="S561" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T561" t="inlineStr">
         <is>
@@ -65291,19 +65277,19 @@
       <c r="AT561" t="inlineStr"/>
       <c r="AW561" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX561" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY561" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>119311630</v>
+        <v>119309475</v>
       </c>
       <c r="B562" t="n">
         <v>78788</v>
@@ -65343,13 +65329,13 @@
         </is>
       </c>
       <c r="Q562" t="n">
-        <v>486944</v>
+        <v>487092</v>
       </c>
       <c r="R562" t="n">
-        <v>7003933</v>
+        <v>7004027</v>
       </c>
       <c r="S562" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T562" t="inlineStr">
         <is>
@@ -65393,22 +65379,22 @@
       <c r="AT562" t="inlineStr"/>
       <c r="AW562" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX562" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY562" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>119312412</v>
+        <v>119309241</v>
       </c>
       <c r="B563" t="n">
-        <v>97003</v>
+        <v>57644</v>
       </c>
       <c r="C563" t="inlineStr">
         <is>
@@ -65417,25 +65403,25 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E563" t="n">
-        <v>221063</v>
+        <v>103021</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I563" t="inlineStr"/>
@@ -65445,13 +65431,13 @@
         </is>
       </c>
       <c r="Q563" t="n">
-        <v>486896</v>
+        <v>487066</v>
       </c>
       <c r="R563" t="n">
-        <v>7003946</v>
+        <v>7004042</v>
       </c>
       <c r="S563" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T563" t="inlineStr">
         <is>

--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -62836,10 +62836,10 @@
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>119311193</v>
+        <v>119311723</v>
       </c>
       <c r="B538" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C538" t="inlineStr">
         <is>
@@ -62848,41 +62848,46 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E538" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P538" t="inlineStr">
         <is>
           <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q538" t="n">
-        <v>487004</v>
+        <v>486946</v>
       </c>
       <c r="R538" t="n">
-        <v>7003923</v>
+        <v>7003956</v>
       </c>
       <c r="S538" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T538" t="inlineStr">
         <is>
@@ -62926,22 +62931,22 @@
       <c r="AT538" t="inlineStr"/>
       <c r="AW538" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX538" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>119312082</v>
+        <v>119312434</v>
       </c>
       <c r="B539" t="n">
-        <v>95313</v>
+        <v>105080</v>
       </c>
       <c r="C539" t="inlineStr">
         <is>
@@ -62954,34 +62959,34 @@
         </is>
       </c>
       <c r="E539" t="n">
-        <v>2809</v>
+        <v>221725</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I539" t="inlineStr"/>
       <c r="P539" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q539" t="n">
-        <v>486946</v>
+        <v>486896</v>
       </c>
       <c r="R539" t="n">
-        <v>7003956</v>
+        <v>7003946</v>
       </c>
       <c r="S539" t="n">
         <v>10</v>
@@ -63028,22 +63033,22 @@
       <c r="AT539" t="inlineStr"/>
       <c r="AW539" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX539" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>119312537</v>
+        <v>119313051</v>
       </c>
       <c r="B540" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C540" t="inlineStr">
         <is>
@@ -63052,41 +63057,41 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E540" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I540" t="inlineStr"/>
       <c r="P540" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q540" t="n">
-        <v>487060</v>
+        <v>486843</v>
       </c>
       <c r="R540" t="n">
-        <v>7004115</v>
+        <v>7004053</v>
       </c>
       <c r="S540" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T540" t="inlineStr">
         <is>
@@ -63130,19 +63135,19 @@
       <c r="AT540" t="inlineStr"/>
       <c r="AW540" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX540" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>119311723</v>
+        <v>119308623</v>
       </c>
       <c r="B541" t="n">
         <v>98079</v>
@@ -63175,7 +63180,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I541" t="inlineStr"/>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K541" t="inlineStr">
         <is>
           <t>överblommad</t>
@@ -63187,13 +63201,13 @@
         </is>
       </c>
       <c r="Q541" t="n">
-        <v>486946</v>
+        <v>487060</v>
       </c>
       <c r="R541" t="n">
-        <v>7003956</v>
+        <v>7004115</v>
       </c>
       <c r="S541" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T541" t="inlineStr">
         <is>
@@ -63249,10 +63263,10 @@
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>119312547</v>
+        <v>119308870</v>
       </c>
       <c r="B542" t="n">
-        <v>97106</v>
+        <v>95313</v>
       </c>
       <c r="C542" t="inlineStr">
         <is>
@@ -63265,27 +63279,27 @@
         </is>
       </c>
       <c r="E542" t="n">
-        <v>222741</v>
+        <v>2809</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I542" t="inlineStr"/>
       <c r="P542" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q542" t="n">
@@ -63351,10 +63365,10 @@
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>119312764</v>
+        <v>119309475</v>
       </c>
       <c r="B543" t="n">
-        <v>97106</v>
+        <v>78788</v>
       </c>
       <c r="C543" t="inlineStr">
         <is>
@@ -63363,38 +63377,38 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E543" t="n">
-        <v>222741</v>
+        <v>6425</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I543" t="inlineStr"/>
       <c r="P543" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q543" t="n">
-        <v>486807</v>
+        <v>487092</v>
       </c>
       <c r="R543" t="n">
-        <v>7003950</v>
+        <v>7004027</v>
       </c>
       <c r="S543" t="n">
         <v>10</v>
@@ -63453,10 +63467,10 @@
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>119311630</v>
+        <v>119312982</v>
       </c>
       <c r="B544" t="n">
-        <v>78788</v>
+        <v>91928</v>
       </c>
       <c r="C544" t="inlineStr">
         <is>
@@ -63465,41 +63479,41 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E544" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I544" t="inlineStr"/>
       <c r="P544" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q544" t="n">
-        <v>486944</v>
+        <v>486822</v>
       </c>
       <c r="R544" t="n">
-        <v>7003933</v>
+        <v>7004015</v>
       </c>
       <c r="S544" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T544" t="inlineStr">
         <is>
@@ -63543,22 +63557,22 @@
       <c r="AT544" t="inlineStr"/>
       <c r="AW544" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX544" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>119312223</v>
+        <v>119311276</v>
       </c>
       <c r="B545" t="n">
-        <v>97106</v>
+        <v>90990</v>
       </c>
       <c r="C545" t="inlineStr">
         <is>
@@ -63567,25 +63581,25 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E545" t="n">
-        <v>222741</v>
+        <v>1202</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I545" t="inlineStr"/>
@@ -63595,13 +63609,13 @@
         </is>
       </c>
       <c r="Q545" t="n">
-        <v>486946</v>
+        <v>487004</v>
       </c>
       <c r="R545" t="n">
-        <v>7003956</v>
+        <v>7003923</v>
       </c>
       <c r="S545" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T545" t="inlineStr">
         <is>
@@ -63645,22 +63659,22 @@
       <c r="AT545" t="inlineStr"/>
       <c r="AW545" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX545" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>119311396</v>
+        <v>119309241</v>
       </c>
       <c r="B546" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C546" t="inlineStr">
         <is>
@@ -63669,41 +63683,41 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E546" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I546" t="inlineStr"/>
       <c r="P546" t="inlineStr">
         <is>
-          <t>Torvalla naturreservat, Torvalla naturreservat, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q546" t="n">
-        <v>486995</v>
+        <v>487066</v>
       </c>
       <c r="R546" t="n">
-        <v>7003925</v>
+        <v>7004042</v>
       </c>
       <c r="S546" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="T546" t="inlineStr">
         <is>
@@ -63759,10 +63773,10 @@
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>119312412</v>
+        <v>119312082</v>
       </c>
       <c r="B547" t="n">
-        <v>97003</v>
+        <v>95313</v>
       </c>
       <c r="C547" t="inlineStr">
         <is>
@@ -63775,34 +63789,34 @@
         </is>
       </c>
       <c r="E547" t="n">
-        <v>221063</v>
+        <v>2809</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>Trådfräken</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>Equisetum scirpoides</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Michx.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I547" t="inlineStr"/>
       <c r="P547" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q547" t="n">
-        <v>486896</v>
+        <v>486946</v>
       </c>
       <c r="R547" t="n">
-        <v>7003946</v>
+        <v>7003956</v>
       </c>
       <c r="S547" t="n">
         <v>10</v>
@@ -63849,22 +63863,22 @@
       <c r="AT547" t="inlineStr"/>
       <c r="AW547" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX547" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>119313051</v>
+        <v>119312764</v>
       </c>
       <c r="B548" t="n">
-        <v>78788</v>
+        <v>97106</v>
       </c>
       <c r="C548" t="inlineStr">
         <is>
@@ -63873,25 +63887,25 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E548" t="n">
-        <v>6425</v>
+        <v>222741</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I548" t="inlineStr"/>
@@ -63901,10 +63915,10 @@
         </is>
       </c>
       <c r="Q548" t="n">
-        <v>486843</v>
+        <v>486807</v>
       </c>
       <c r="R548" t="n">
-        <v>7004053</v>
+        <v>7003950</v>
       </c>
       <c r="S548" t="n">
         <v>10</v>
@@ -63963,10 +63977,10 @@
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>119310979</v>
+        <v>119309185</v>
       </c>
       <c r="B549" t="n">
-        <v>91928</v>
+        <v>98079</v>
       </c>
       <c r="C549" t="inlineStr">
         <is>
@@ -63975,41 +63989,41 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E549" t="n">
-        <v>4769</v>
+        <v>220787</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I549" t="inlineStr"/>
       <c r="P549" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q549" t="n">
-        <v>487043</v>
+        <v>487054</v>
       </c>
       <c r="R549" t="n">
-        <v>7003935</v>
+        <v>7004058</v>
       </c>
       <c r="S549" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T549" t="inlineStr">
         <is>
@@ -64065,10 +64079,10 @@
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>119309504</v>
+        <v>119312547</v>
       </c>
       <c r="B550" t="n">
-        <v>98079</v>
+        <v>97106</v>
       </c>
       <c r="C550" t="inlineStr">
         <is>
@@ -64077,25 +64091,25 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E550" t="n">
-        <v>220787</v>
+        <v>222741</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I550" t="inlineStr"/>
@@ -64105,10 +64119,10 @@
         </is>
       </c>
       <c r="Q550" t="n">
-        <v>487056</v>
+        <v>487060</v>
       </c>
       <c r="R550" t="n">
-        <v>7004063</v>
+        <v>7004115</v>
       </c>
       <c r="S550" t="n">
         <v>3</v>
@@ -64167,10 +64181,10 @@
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>119313079</v>
+        <v>119312223</v>
       </c>
       <c r="B551" t="n">
-        <v>78788</v>
+        <v>97106</v>
       </c>
       <c r="C551" t="inlineStr">
         <is>
@@ -64179,38 +64193,38 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E551" t="n">
-        <v>6425</v>
+        <v>222741</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I551" t="inlineStr"/>
       <c r="P551" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q551" t="n">
-        <v>486834</v>
+        <v>486946</v>
       </c>
       <c r="R551" t="n">
-        <v>7004097</v>
+        <v>7003956</v>
       </c>
       <c r="S551" t="n">
         <v>10</v>
@@ -64257,22 +64271,22 @@
       <c r="AT551" t="inlineStr"/>
       <c r="AW551" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX551" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY551" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>119311857</v>
+        <v>119311630</v>
       </c>
       <c r="B552" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C552" t="inlineStr">
         <is>
@@ -64285,37 +64299,37 @@
         </is>
       </c>
       <c r="E552" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I552" t="inlineStr"/>
       <c r="P552" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q552" t="n">
-        <v>486943</v>
+        <v>486944</v>
       </c>
       <c r="R552" t="n">
-        <v>7003953</v>
+        <v>7003933</v>
       </c>
       <c r="S552" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T552" t="inlineStr">
         <is>
@@ -64359,22 +64373,22 @@
       <c r="AT552" t="inlineStr"/>
       <c r="AW552" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX552" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY552" t="inlineStr"/>
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>119312531</v>
+        <v>119309504</v>
       </c>
       <c r="B553" t="n">
-        <v>105080</v>
+        <v>98079</v>
       </c>
       <c r="C553" t="inlineStr">
         <is>
@@ -64383,41 +64397,41 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E553" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I553" t="inlineStr"/>
       <c r="P553" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q553" t="n">
-        <v>486896</v>
+        <v>487056</v>
       </c>
       <c r="R553" t="n">
-        <v>7003946</v>
+        <v>7004063</v>
       </c>
       <c r="S553" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T553" t="inlineStr">
         <is>
@@ -64461,22 +64475,22 @@
       <c r="AT553" t="inlineStr"/>
       <c r="AW553" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX553" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY553" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>119308870</v>
+        <v>119312412</v>
       </c>
       <c r="B554" t="n">
-        <v>95313</v>
+        <v>97003</v>
       </c>
       <c r="C554" t="inlineStr">
         <is>
@@ -64489,37 +64503,37 @@
         </is>
       </c>
       <c r="E554" t="n">
-        <v>2809</v>
+        <v>221063</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Trådfräken</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Equisetum scirpoides</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Michx.</t>
         </is>
       </c>
       <c r="I554" t="inlineStr"/>
       <c r="P554" t="inlineStr">
         <is>
-          <t>Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q554" t="n">
-        <v>487060</v>
+        <v>486896</v>
       </c>
       <c r="R554" t="n">
-        <v>7004115</v>
+        <v>7003946</v>
       </c>
       <c r="S554" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T554" t="inlineStr">
         <is>
@@ -64563,19 +64577,19 @@
       <c r="AT554" t="inlineStr"/>
       <c r="AW554" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX554" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY554" t="inlineStr"/>
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>119312982</v>
+        <v>119310979</v>
       </c>
       <c r="B555" t="n">
         <v>91928</v>
@@ -64611,14 +64625,14 @@
       <c r="I555" t="inlineStr"/>
       <c r="P555" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q555" t="n">
-        <v>486822</v>
+        <v>487043</v>
       </c>
       <c r="R555" t="n">
-        <v>7004015</v>
+        <v>7003935</v>
       </c>
       <c r="S555" t="n">
         <v>20</v>
@@ -64677,10 +64691,10 @@
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>119311276</v>
+        <v>119310718</v>
       </c>
       <c r="B556" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C556" t="inlineStr">
         <is>
@@ -64693,21 +64707,21 @@
         </is>
       </c>
       <c r="E556" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I556" t="inlineStr"/>
@@ -64717,13 +64731,13 @@
         </is>
       </c>
       <c r="Q556" t="n">
-        <v>487004</v>
+        <v>487060</v>
       </c>
       <c r="R556" t="n">
-        <v>7003923</v>
+        <v>7004115</v>
       </c>
       <c r="S556" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T556" t="inlineStr">
         <is>
@@ -64767,22 +64781,22 @@
       <c r="AT556" t="inlineStr"/>
       <c r="AW556" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX556" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>119309185</v>
+        <v>119308823</v>
       </c>
       <c r="B557" t="n">
-        <v>98079</v>
+        <v>91928</v>
       </c>
       <c r="C557" t="inlineStr">
         <is>
@@ -64791,41 +64805,41 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E557" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I557" t="inlineStr"/>
       <c r="P557" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q557" t="n">
-        <v>487054</v>
+        <v>487060</v>
       </c>
       <c r="R557" t="n">
-        <v>7004058</v>
+        <v>7004115</v>
       </c>
       <c r="S557" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T557" t="inlineStr">
         <is>
@@ -64869,12 +64883,12 @@
       <c r="AT557" t="inlineStr"/>
       <c r="AW557" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX557" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY557" t="inlineStr"/>
@@ -64983,10 +64997,10 @@
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>119310718</v>
+        <v>119312398</v>
       </c>
       <c r="B559" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C559" t="inlineStr">
         <is>
@@ -64995,41 +65009,41 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E559" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I559" t="inlineStr"/>
       <c r="P559" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q559" t="n">
-        <v>487060</v>
+        <v>486896</v>
       </c>
       <c r="R559" t="n">
-        <v>7004115</v>
+        <v>7003946</v>
       </c>
       <c r="S559" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T559" t="inlineStr">
         <is>
@@ -65073,22 +65087,22 @@
       <c r="AT559" t="inlineStr"/>
       <c r="AW559" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX559" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>119308823</v>
+        <v>119313079</v>
       </c>
       <c r="B560" t="n">
-        <v>91928</v>
+        <v>78788</v>
       </c>
       <c r="C560" t="inlineStr">
         <is>
@@ -65097,41 +65111,41 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E560" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I560" t="inlineStr"/>
       <c r="P560" t="inlineStr">
         <is>
-          <t>Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q560" t="n">
-        <v>487060</v>
+        <v>486834</v>
       </c>
       <c r="R560" t="n">
-        <v>7004115</v>
+        <v>7004097</v>
       </c>
       <c r="S560" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T560" t="inlineStr">
         <is>
@@ -65175,22 +65189,22 @@
       <c r="AT560" t="inlineStr"/>
       <c r="AW560" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX560" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY560" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>119312398</v>
+        <v>119311193</v>
       </c>
       <c r="B561" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C561" t="inlineStr">
         <is>
@@ -65199,41 +65213,41 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E561" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I561" t="inlineStr"/>
       <c r="P561" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q561" t="n">
-        <v>486896</v>
+        <v>487004</v>
       </c>
       <c r="R561" t="n">
-        <v>7003946</v>
+        <v>7003923</v>
       </c>
       <c r="S561" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T561" t="inlineStr">
         <is>
@@ -65289,10 +65303,10 @@
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>119309475</v>
+        <v>119311396</v>
       </c>
       <c r="B562" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C562" t="inlineStr">
         <is>
@@ -65301,41 +65315,41 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E562" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I562" t="inlineStr"/>
       <c r="P562" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Torvalla naturreservat, Torvalla naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q562" t="n">
-        <v>487092</v>
+        <v>486995</v>
       </c>
       <c r="R562" t="n">
-        <v>7004027</v>
+        <v>7003925</v>
       </c>
       <c r="S562" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T562" t="inlineStr">
         <is>
@@ -65391,10 +65405,10 @@
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>119309241</v>
+        <v>119311857</v>
       </c>
       <c r="B563" t="n">
-        <v>57644</v>
+        <v>90990</v>
       </c>
       <c r="C563" t="inlineStr">
         <is>
@@ -65407,21 +65421,21 @@
         </is>
       </c>
       <c r="E563" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I563" t="inlineStr"/>
@@ -65431,13 +65445,13 @@
         </is>
       </c>
       <c r="Q563" t="n">
-        <v>487066</v>
+        <v>486943</v>
       </c>
       <c r="R563" t="n">
-        <v>7004042</v>
+        <v>7003953</v>
       </c>
       <c r="S563" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="T563" t="inlineStr">
         <is>

--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -62836,10 +62836,10 @@
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>119311723</v>
+        <v>119309475</v>
       </c>
       <c r="B538" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C538" t="inlineStr">
         <is>
@@ -62848,46 +62848,41 @@
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E538" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I538" t="inlineStr"/>
-      <c r="K538" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P538" t="inlineStr">
         <is>
           <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q538" t="n">
-        <v>486946</v>
+        <v>487092</v>
       </c>
       <c r="R538" t="n">
-        <v>7003956</v>
+        <v>7004027</v>
       </c>
       <c r="S538" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T538" t="inlineStr">
         <is>
@@ -62931,22 +62926,22 @@
       <c r="AT538" t="inlineStr"/>
       <c r="AW538" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX538" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>119312434</v>
+        <v>119308623</v>
       </c>
       <c r="B539" t="n">
-        <v>105080</v>
+        <v>98079</v>
       </c>
       <c r="C539" t="inlineStr">
         <is>
@@ -62955,41 +62950,55 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E539" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I539" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P539" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q539" t="n">
-        <v>486896</v>
+        <v>487060</v>
       </c>
       <c r="R539" t="n">
-        <v>7003946</v>
+        <v>7004115</v>
       </c>
       <c r="S539" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T539" t="inlineStr">
         <is>
@@ -63033,22 +63042,22 @@
       <c r="AT539" t="inlineStr"/>
       <c r="AW539" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX539" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>119313051</v>
+        <v>119308870</v>
       </c>
       <c r="B540" t="n">
-        <v>78788</v>
+        <v>95313</v>
       </c>
       <c r="C540" t="inlineStr">
         <is>
@@ -63057,41 +63066,41 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E540" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I540" t="inlineStr"/>
       <c r="P540" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q540" t="n">
-        <v>486843</v>
+        <v>487060</v>
       </c>
       <c r="R540" t="n">
-        <v>7004053</v>
+        <v>7004115</v>
       </c>
       <c r="S540" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T540" t="inlineStr">
         <is>
@@ -63135,22 +63144,22 @@
       <c r="AT540" t="inlineStr"/>
       <c r="AW540" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX540" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>119308623</v>
+        <v>119310718</v>
       </c>
       <c r="B541" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C541" t="inlineStr">
         <is>
@@ -63159,42 +63168,28 @@
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E541" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I541" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J541" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K541" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr"/>
       <c r="P541" t="inlineStr">
         <is>
           <t>Verksmon, Verksmon, Jmt</t>
@@ -63207,7 +63202,7 @@
         <v>7004115</v>
       </c>
       <c r="S541" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T541" t="inlineStr">
         <is>
@@ -63263,10 +63258,10 @@
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>119308870</v>
+        <v>119309241</v>
       </c>
       <c r="B542" t="n">
-        <v>95313</v>
+        <v>57644</v>
       </c>
       <c r="C542" t="inlineStr">
         <is>
@@ -63275,41 +63270,41 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E542" t="n">
-        <v>2809</v>
+        <v>103021</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I542" t="inlineStr"/>
       <c r="P542" t="inlineStr">
         <is>
-          <t>Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q542" t="n">
-        <v>487060</v>
+        <v>487066</v>
       </c>
       <c r="R542" t="n">
-        <v>7004115</v>
+        <v>7004042</v>
       </c>
       <c r="S542" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="T542" t="inlineStr">
         <is>
@@ -63353,22 +63348,22 @@
       <c r="AT542" t="inlineStr"/>
       <c r="AW542" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX542" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>119309475</v>
+        <v>119312982</v>
       </c>
       <c r="B543" t="n">
-        <v>78788</v>
+        <v>91928</v>
       </c>
       <c r="C543" t="inlineStr">
         <is>
@@ -63377,41 +63372,41 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E543" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I543" t="inlineStr"/>
       <c r="P543" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q543" t="n">
-        <v>487092</v>
+        <v>486822</v>
       </c>
       <c r="R543" t="n">
-        <v>7004027</v>
+        <v>7004015</v>
       </c>
       <c r="S543" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T543" t="inlineStr">
         <is>
@@ -63467,10 +63462,10 @@
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>119312982</v>
+        <v>119311193</v>
       </c>
       <c r="B544" t="n">
-        <v>91928</v>
+        <v>78788</v>
       </c>
       <c r="C544" t="inlineStr">
         <is>
@@ -63479,38 +63474,38 @@
       </c>
       <c r="D544" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E544" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I544" t="inlineStr"/>
       <c r="P544" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q544" t="n">
-        <v>486822</v>
+        <v>487004</v>
       </c>
       <c r="R544" t="n">
-        <v>7004015</v>
+        <v>7003923</v>
       </c>
       <c r="S544" t="n">
         <v>20</v>
@@ -63569,10 +63564,10 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>119311276</v>
+        <v>119311723</v>
       </c>
       <c r="B545" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C545" t="inlineStr">
         <is>
@@ -63581,41 +63576,46 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E545" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P545" t="inlineStr">
         <is>
           <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q545" t="n">
-        <v>487004</v>
+        <v>486946</v>
       </c>
       <c r="R545" t="n">
-        <v>7003923</v>
+        <v>7003956</v>
       </c>
       <c r="S545" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T545" t="inlineStr">
         <is>
@@ -63659,22 +63659,22 @@
       <c r="AT545" t="inlineStr"/>
       <c r="AW545" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX545" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>119309241</v>
+        <v>119312398</v>
       </c>
       <c r="B546" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C546" t="inlineStr">
         <is>
@@ -63683,25 +63683,25 @@
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E546" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I546" t="inlineStr"/>
@@ -63711,13 +63711,13 @@
         </is>
       </c>
       <c r="Q546" t="n">
-        <v>487066</v>
+        <v>486896</v>
       </c>
       <c r="R546" t="n">
-        <v>7004042</v>
+        <v>7003946</v>
       </c>
       <c r="S546" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T546" t="inlineStr">
         <is>
@@ -63773,10 +63773,10 @@
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>119312082</v>
+        <v>119312547</v>
       </c>
       <c r="B547" t="n">
-        <v>95313</v>
+        <v>97106</v>
       </c>
       <c r="C547" t="inlineStr">
         <is>
@@ -63789,21 +63789,21 @@
         </is>
       </c>
       <c r="E547" t="n">
-        <v>2809</v>
+        <v>222741</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I547" t="inlineStr"/>
@@ -63813,13 +63813,13 @@
         </is>
       </c>
       <c r="Q547" t="n">
-        <v>486946</v>
+        <v>487060</v>
       </c>
       <c r="R547" t="n">
-        <v>7003956</v>
+        <v>7004115</v>
       </c>
       <c r="S547" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T547" t="inlineStr">
         <is>
@@ -63875,10 +63875,10 @@
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>119312764</v>
+        <v>119308823</v>
       </c>
       <c r="B548" t="n">
-        <v>97106</v>
+        <v>91928</v>
       </c>
       <c r="C548" t="inlineStr">
         <is>
@@ -63891,37 +63891,37 @@
         </is>
       </c>
       <c r="E548" t="n">
-        <v>222741</v>
+        <v>4769</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I548" t="inlineStr"/>
       <c r="P548" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q548" t="n">
-        <v>486807</v>
+        <v>487060</v>
       </c>
       <c r="R548" t="n">
-        <v>7003950</v>
+        <v>7004115</v>
       </c>
       <c r="S548" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T548" t="inlineStr">
         <is>
@@ -63965,22 +63965,22 @@
       <c r="AT548" t="inlineStr"/>
       <c r="AW548" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX548" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>119309185</v>
+        <v>119312434</v>
       </c>
       <c r="B549" t="n">
-        <v>98079</v>
+        <v>105080</v>
       </c>
       <c r="C549" t="inlineStr">
         <is>
@@ -63989,25 +63989,25 @@
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E549" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I549" t="inlineStr"/>
@@ -64017,10 +64017,10 @@
         </is>
       </c>
       <c r="Q549" t="n">
-        <v>487054</v>
+        <v>486896</v>
       </c>
       <c r="R549" t="n">
-        <v>7004058</v>
+        <v>7003946</v>
       </c>
       <c r="S549" t="n">
         <v>10</v>
@@ -64079,10 +64079,10 @@
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>119312547</v>
+        <v>119312923</v>
       </c>
       <c r="B550" t="n">
-        <v>97106</v>
+        <v>57644</v>
       </c>
       <c r="C550" t="inlineStr">
         <is>
@@ -64091,25 +64091,25 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E550" t="n">
-        <v>222741</v>
+        <v>103021</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I550" t="inlineStr"/>
@@ -64125,7 +64125,7 @@
         <v>7004115</v>
       </c>
       <c r="S550" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T550" t="inlineStr">
         <is>
@@ -64181,10 +64181,10 @@
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>119312223</v>
+        <v>119309504</v>
       </c>
       <c r="B551" t="n">
-        <v>97106</v>
+        <v>98079</v>
       </c>
       <c r="C551" t="inlineStr">
         <is>
@@ -64193,25 +64193,25 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E551" t="n">
-        <v>222741</v>
+        <v>220787</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I551" t="inlineStr"/>
@@ -64221,13 +64221,13 @@
         </is>
       </c>
       <c r="Q551" t="n">
-        <v>486946</v>
+        <v>487056</v>
       </c>
       <c r="R551" t="n">
-        <v>7003956</v>
+        <v>7004063</v>
       </c>
       <c r="S551" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T551" t="inlineStr">
         <is>
@@ -64385,10 +64385,10 @@
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>119309504</v>
+        <v>119311857</v>
       </c>
       <c r="B553" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C553" t="inlineStr">
         <is>
@@ -64397,41 +64397,41 @@
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E553" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I553" t="inlineStr"/>
       <c r="P553" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q553" t="n">
-        <v>487056</v>
+        <v>486943</v>
       </c>
       <c r="R553" t="n">
-        <v>7004063</v>
+        <v>7003953</v>
       </c>
       <c r="S553" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="T553" t="inlineStr">
         <is>
@@ -64475,12 +64475,12 @@
       <c r="AT553" t="inlineStr"/>
       <c r="AW553" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX553" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY553" t="inlineStr"/>
@@ -64589,10 +64589,10 @@
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>119310979</v>
+        <v>119312764</v>
       </c>
       <c r="B555" t="n">
-        <v>91928</v>
+        <v>97106</v>
       </c>
       <c r="C555" t="inlineStr">
         <is>
@@ -64605,37 +64605,37 @@
         </is>
       </c>
       <c r="E555" t="n">
-        <v>4769</v>
+        <v>222741</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I555" t="inlineStr"/>
       <c r="P555" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q555" t="n">
-        <v>487043</v>
+        <v>486807</v>
       </c>
       <c r="R555" t="n">
-        <v>7003935</v>
+        <v>7003950</v>
       </c>
       <c r="S555" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T555" t="inlineStr">
         <is>
@@ -64691,10 +64691,10 @@
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>119310718</v>
+        <v>119309185</v>
       </c>
       <c r="B556" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C556" t="inlineStr">
         <is>
@@ -64703,41 +64703,41 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E556" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I556" t="inlineStr"/>
       <c r="P556" t="inlineStr">
         <is>
-          <t>Verksmon, Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q556" t="n">
-        <v>487060</v>
+        <v>487054</v>
       </c>
       <c r="R556" t="n">
-        <v>7004115</v>
+        <v>7004058</v>
       </c>
       <c r="S556" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T556" t="inlineStr">
         <is>
@@ -64781,22 +64781,22 @@
       <c r="AT556" t="inlineStr"/>
       <c r="AW556" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX556" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY556" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>119308823</v>
+        <v>119313051</v>
       </c>
       <c r="B557" t="n">
-        <v>91928</v>
+        <v>78788</v>
       </c>
       <c r="C557" t="inlineStr">
         <is>
@@ -64805,41 +64805,41 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E557" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I557" t="inlineStr"/>
       <c r="P557" t="inlineStr">
         <is>
-          <t>Verksmon, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q557" t="n">
-        <v>487060</v>
+        <v>486843</v>
       </c>
       <c r="R557" t="n">
-        <v>7004115</v>
+        <v>7004053</v>
       </c>
       <c r="S557" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T557" t="inlineStr">
         <is>
@@ -64883,22 +64883,22 @@
       <c r="AT557" t="inlineStr"/>
       <c r="AW557" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX557" t="inlineStr">
         <is>
-          <t>Jana Novak</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY557" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>119312923</v>
+        <v>119312223</v>
       </c>
       <c r="B558" t="n">
-        <v>57644</v>
+        <v>97106</v>
       </c>
       <c r="C558" t="inlineStr">
         <is>
@@ -64907,25 +64907,25 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E558" t="n">
-        <v>103021</v>
+        <v>222741</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I558" t="inlineStr"/>
@@ -64935,10 +64935,10 @@
         </is>
       </c>
       <c r="Q558" t="n">
-        <v>487060</v>
+        <v>486946</v>
       </c>
       <c r="R558" t="n">
-        <v>7004115</v>
+        <v>7003956</v>
       </c>
       <c r="S558" t="n">
         <v>10</v>
@@ -64997,10 +64997,10 @@
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>119312398</v>
+        <v>119312082</v>
       </c>
       <c r="B559" t="n">
-        <v>98079</v>
+        <v>95313</v>
       </c>
       <c r="C559" t="inlineStr">
         <is>
@@ -65009,38 +65009,38 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E559" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I559" t="inlineStr"/>
       <c r="P559" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q559" t="n">
-        <v>486896</v>
+        <v>486946</v>
       </c>
       <c r="R559" t="n">
-        <v>7003946</v>
+        <v>7003956</v>
       </c>
       <c r="S559" t="n">
         <v>10</v>
@@ -65087,22 +65087,22 @@
       <c r="AT559" t="inlineStr"/>
       <c r="AW559" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AX559" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Jana Novak</t>
         </is>
       </c>
       <c r="AY559" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>119313079</v>
+        <v>119311276</v>
       </c>
       <c r="B560" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C560" t="inlineStr">
         <is>
@@ -65115,37 +65115,37 @@
         </is>
       </c>
       <c r="E560" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I560" t="inlineStr"/>
       <c r="P560" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Verksmon, Verksmon, Jmt</t>
         </is>
       </c>
       <c r="Q560" t="n">
-        <v>486834</v>
+        <v>487004</v>
       </c>
       <c r="R560" t="n">
-        <v>7004097</v>
+        <v>7003923</v>
       </c>
       <c r="S560" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T560" t="inlineStr">
         <is>
@@ -65201,10 +65201,10 @@
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>119311193</v>
+        <v>119310979</v>
       </c>
       <c r="B561" t="n">
-        <v>78788</v>
+        <v>91928</v>
       </c>
       <c r="C561" t="inlineStr">
         <is>
@@ -65213,25 +65213,25 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E561" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I561" t="inlineStr"/>
@@ -65241,10 +65241,10 @@
         </is>
       </c>
       <c r="Q561" t="n">
-        <v>487004</v>
+        <v>487043</v>
       </c>
       <c r="R561" t="n">
-        <v>7003923</v>
+        <v>7003935</v>
       </c>
       <c r="S561" t="n">
         <v>20</v>
@@ -65303,10 +65303,10 @@
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>119311396</v>
+        <v>119313079</v>
       </c>
       <c r="B562" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C562" t="inlineStr">
         <is>
@@ -65315,41 +65315,41 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E562" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I562" t="inlineStr"/>
       <c r="P562" t="inlineStr">
         <is>
-          <t>Torvalla naturreservat, Torvalla naturreservat, Jmt</t>
+          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q562" t="n">
-        <v>486995</v>
+        <v>486834</v>
       </c>
       <c r="R562" t="n">
-        <v>7003925</v>
+        <v>7004097</v>
       </c>
       <c r="S562" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T562" t="inlineStr">
         <is>
@@ -65405,10 +65405,10 @@
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>119311857</v>
+        <v>119311396</v>
       </c>
       <c r="B563" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C563" t="inlineStr">
         <is>
@@ -65417,38 +65417,38 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E563" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I563" t="inlineStr"/>
       <c r="P563" t="inlineStr">
         <is>
-          <t>Ol-Johansbodarna, Ol-Johansbodarna, Jmt</t>
+          <t>Torvalla naturreservat, Torvalla naturreservat, Jmt</t>
         </is>
       </c>
       <c r="Q563" t="n">
-        <v>486943</v>
+        <v>486995</v>
       </c>
       <c r="R563" t="n">
-        <v>7003953</v>
+        <v>7003925</v>
       </c>
       <c r="S563" t="n">
         <v>20</v>

--- a/artfynd/A 51192-2019 artfynd.xlsx
+++ b/artfynd/A 51192-2019 artfynd.xlsx
@@ -64079,10 +64079,10 @@
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>119312923</v>
+        <v>119309504</v>
       </c>
       <c r="B550" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C550" t="inlineStr">
         <is>
@@ -64091,25 +64091,25 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E550" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I550" t="inlineStr"/>
@@ -64119,13 +64119,13 @@
         </is>
       </c>
       <c r="Q550" t="n">
-        <v>487060</v>
+        <v>487056</v>
       </c>
       <c r="R550" t="n">
-        <v>7004115</v>
+        <v>7004063</v>
       </c>
       <c r="S550" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T550" t="inlineStr">
         <is>
@@ -64181,10 +64181,10 @@
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>119309504</v>
+        <v>119312923</v>
       </c>
       <c r="B551" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C551" t="inlineStr">
         <is>
@@ -64193,25 +64193,25 @@
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E551" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I551" t="inlineStr"/>
@@ -64221,13 +64221,13 @@
         </is>
       </c>
       <c r="Q551" t="n">
-        <v>487056</v>
+        <v>487060</v>
       </c>
       <c r="R551" t="n">
-        <v>7004063</v>
+        <v>7004115</v>
       </c>
       <c r="S551" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T551" t="inlineStr">
         <is>
@@ -64691,10 +64691,10 @@
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>119309185</v>
+        <v>119313051</v>
       </c>
       <c r="B556" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C556" t="inlineStr">
         <is>
@@ -64703,25 +64703,25 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E556" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I556" t="inlineStr"/>
@@ -64731,10 +64731,10 @@
         </is>
       </c>
       <c r="Q556" t="n">
-        <v>487054</v>
+        <v>486843</v>
       </c>
       <c r="R556" t="n">
-        <v>7004058</v>
+        <v>7004053</v>
       </c>
       <c r="S556" t="n">
         <v>10</v>
@@ -64793,10 +64793,10 @@
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>119313051</v>
+        <v>119309185</v>
       </c>
       <c r="B557" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C557" t="inlineStr">
         <is>
@@ -64805,25 +64805,25 @@
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E557" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I557" t="inlineStr"/>
@@ -64833,10 +64833,10 @@
         </is>
       </c>
       <c r="Q557" t="n">
-        <v>486843</v>
+        <v>487054</v>
       </c>
       <c r="R557" t="n">
-        <v>7004053</v>
+        <v>7004058</v>
       </c>
       <c r="S557" t="n">
         <v>10</v>
